--- a/data/nzd0574/nzd0574.xlsx
+++ b/data/nzd0574/nzd0574.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S453"/>
+  <dimension ref="A1:S455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28999,6 +28999,132 @@
         <v>257</v>
       </c>
       <c r="S453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:18+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>237.39</v>
+      </c>
+      <c r="C454" t="n">
+        <v>239.21</v>
+      </c>
+      <c r="D454" t="n">
+        <v>253.32</v>
+      </c>
+      <c r="E454" t="n">
+        <v>249.27</v>
+      </c>
+      <c r="F454" t="n">
+        <v>248.22</v>
+      </c>
+      <c r="G454" t="n">
+        <v>248.53</v>
+      </c>
+      <c r="H454" t="n">
+        <v>248.45</v>
+      </c>
+      <c r="I454" t="n">
+        <v>252.09</v>
+      </c>
+      <c r="J454" t="n">
+        <v>257.07</v>
+      </c>
+      <c r="K454" t="n">
+        <v>254.06</v>
+      </c>
+      <c r="L454" t="n">
+        <v>255.4</v>
+      </c>
+      <c r="M454" t="n">
+        <v>252.52</v>
+      </c>
+      <c r="N454" t="n">
+        <v>251.93</v>
+      </c>
+      <c r="O454" t="n">
+        <v>247.53</v>
+      </c>
+      <c r="P454" t="n">
+        <v>249.9</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>255.74</v>
+      </c>
+      <c r="R454" t="n">
+        <v>261.95</v>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:13:18+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>234.96</v>
+      </c>
+      <c r="C455" t="n">
+        <v>236.72</v>
+      </c>
+      <c r="D455" t="n">
+        <v>251.1</v>
+      </c>
+      <c r="E455" t="n">
+        <v>247</v>
+      </c>
+      <c r="F455" t="n">
+        <v>245.49</v>
+      </c>
+      <c r="G455" t="n">
+        <v>246.84</v>
+      </c>
+      <c r="H455" t="n">
+        <v>246.3</v>
+      </c>
+      <c r="I455" t="n">
+        <v>249.65</v>
+      </c>
+      <c r="J455" t="n">
+        <v>254.71</v>
+      </c>
+      <c r="K455" t="n">
+        <v>252.01</v>
+      </c>
+      <c r="L455" t="n">
+        <v>253.05</v>
+      </c>
+      <c r="M455" t="n">
+        <v>250.94</v>
+      </c>
+      <c r="N455" t="n">
+        <v>250.11</v>
+      </c>
+      <c r="O455" t="n">
+        <v>246.12</v>
+      </c>
+      <c r="P455" t="n">
+        <v>249.52</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>255.78</v>
+      </c>
+      <c r="R455" t="n">
+        <v>261.09</v>
+      </c>
+      <c r="S455" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29015,7 +29141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B454"/>
+  <dimension ref="A1:B456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33558,6 +33684,26 @@
       </c>
       <c r="B454" t="n">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -33720,28 +33866,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1914966254121855</v>
+        <v>0.1899923472105069</v>
       </c>
       <c r="J2" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K2" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L2" t="n">
-        <v>0.108077305252997</v>
+        <v>0.1074063983993804</v>
       </c>
       <c r="M2" t="n">
-        <v>3.301413247402984</v>
+        <v>3.293991419382248</v>
       </c>
       <c r="N2" t="n">
-        <v>16.7338101238266</v>
+        <v>16.67919094025876</v>
       </c>
       <c r="O2" t="n">
-        <v>4.090697999587185</v>
+        <v>4.084016520566335</v>
       </c>
       <c r="P2" t="n">
-        <v>232.8047625993416</v>
+        <v>232.8203348852874</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33792,28 +33938,28 @@
         <v>0.0863</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05442404083491216</v>
+        <v>0.05492667717562882</v>
       </c>
       <c r="J3" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K3" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0102495201917826</v>
+        <v>0.01053539894327293</v>
       </c>
       <c r="M3" t="n">
-        <v>3.322418328246652</v>
+        <v>3.313488680893711</v>
       </c>
       <c r="N3" t="n">
-        <v>15.81552572105057</v>
+        <v>15.75415370463539</v>
       </c>
       <c r="O3" t="n">
-        <v>3.976873862853909</v>
+        <v>3.969150249692671</v>
       </c>
       <c r="P3" t="n">
-        <v>235.9523050501324</v>
+        <v>235.9471161001999</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33864,28 +34010,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01052735847496735</v>
+        <v>0.01290013029533877</v>
       </c>
       <c r="J4" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K4" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003653175320129654</v>
+        <v>0.0005527104638958225</v>
       </c>
       <c r="M4" t="n">
-        <v>3.417109831846035</v>
+        <v>3.41399631900316</v>
       </c>
       <c r="N4" t="n">
-        <v>16.76831807892609</v>
+        <v>16.73129475044498</v>
       </c>
       <c r="O4" t="n">
-        <v>4.094913683940859</v>
+        <v>4.090390537643683</v>
       </c>
       <c r="P4" t="n">
-        <v>249.2408719623285</v>
+        <v>249.2163352967679</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33936,28 +34082,28 @@
         <v>0.0901</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02250752344965367</v>
+        <v>-0.02097163609778561</v>
       </c>
       <c r="J5" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K5" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001690942878467383</v>
+        <v>0.001481318796738518</v>
       </c>
       <c r="M5" t="n">
-        <v>3.293860252640848</v>
+        <v>3.287221186597892</v>
       </c>
       <c r="N5" t="n">
-        <v>16.53755785001817</v>
+        <v>16.48357603460979</v>
       </c>
       <c r="O5" t="n">
-        <v>4.066639626278454</v>
+        <v>4.059997048596191</v>
       </c>
       <c r="P5" t="n">
-        <v>246.9908154903858</v>
+        <v>246.9749366034419</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34008,28 +34154,28 @@
         <v>0.0813</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08165740572772215</v>
+        <v>-0.07980540040280369</v>
       </c>
       <c r="J6" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K6" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02076427524207181</v>
+        <v>0.02001491611606532</v>
       </c>
       <c r="M6" t="n">
-        <v>3.383358589025628</v>
+        <v>3.377989388324098</v>
       </c>
       <c r="N6" t="n">
-        <v>17.38767475965638</v>
+        <v>17.33841531485085</v>
       </c>
       <c r="O6" t="n">
-        <v>4.169853086099843</v>
+        <v>4.163942280441799</v>
       </c>
       <c r="P6" t="n">
-        <v>246.9169757379309</v>
+        <v>246.8978285699023</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34080,28 +34226,28 @@
         <v>0.0902</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1559516750355852</v>
+        <v>-0.1535656602889079</v>
       </c>
       <c r="J7" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K7" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06530931717124477</v>
+        <v>0.0639363658104275</v>
       </c>
       <c r="M7" t="n">
-        <v>3.445275748234834</v>
+        <v>3.441471794371116</v>
       </c>
       <c r="N7" t="n">
-        <v>19.2465431439548</v>
+        <v>19.19662131641995</v>
       </c>
       <c r="O7" t="n">
-        <v>4.387088230700951</v>
+        <v>4.381394905326379</v>
       </c>
       <c r="P7" t="n">
-        <v>249.1103089773725</v>
+        <v>249.085632984768</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34152,28 +34298,28 @@
         <v>0.0733</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1906445362366437</v>
+        <v>-0.1900787238127319</v>
       </c>
       <c r="J8" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K8" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1177085236625837</v>
+        <v>0.1180767132758598</v>
       </c>
       <c r="M8" t="n">
-        <v>3.068274935356117</v>
+        <v>3.059640070142374</v>
       </c>
       <c r="N8" t="n">
-        <v>15.06373880866066</v>
+        <v>15.00419562247538</v>
       </c>
       <c r="O8" t="n">
-        <v>3.881203268145158</v>
+        <v>3.873524960869025</v>
       </c>
       <c r="P8" t="n">
-        <v>251.7816739985117</v>
+        <v>251.7758299174149</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34224,28 +34370,28 @@
         <v>0.0664</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2231374516515158</v>
+        <v>-0.2222969318392278</v>
       </c>
       <c r="J9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1195790631300048</v>
+        <v>0.1197764337908488</v>
       </c>
       <c r="M9" t="n">
-        <v>3.584348788438017</v>
+        <v>3.574232495707349</v>
       </c>
       <c r="N9" t="n">
-        <v>20.27029329342556</v>
+        <v>20.19145889581563</v>
       </c>
       <c r="O9" t="n">
-        <v>4.502254245755736</v>
+        <v>4.493490725017202</v>
       </c>
       <c r="P9" t="n">
-        <v>255.8282997695892</v>
+        <v>255.8196151227124</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34296,28 +34442,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.153427899873432</v>
+        <v>-0.1508402753753969</v>
       </c>
       <c r="J10" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K10" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05309913749340855</v>
+        <v>0.05180900551871004</v>
       </c>
       <c r="M10" t="n">
-        <v>3.731002704637114</v>
+        <v>3.726652761598036</v>
       </c>
       <c r="N10" t="n">
-        <v>23.21162821875653</v>
+        <v>23.15284434450932</v>
       </c>
       <c r="O10" t="n">
-        <v>4.817844769059764</v>
+        <v>4.811740261538367</v>
       </c>
       <c r="P10" t="n">
-        <v>257.019925943893</v>
+        <v>256.9931672155395</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34368,28 +34514,28 @@
         <v>0.0576</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1284505970624908</v>
+        <v>-0.1281179639914296</v>
       </c>
       <c r="J11" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K11" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03784211728183462</v>
+        <v>0.03800734924334381</v>
       </c>
       <c r="M11" t="n">
-        <v>3.715712466762201</v>
+        <v>3.703802895340449</v>
       </c>
       <c r="N11" t="n">
-        <v>23.19653138888124</v>
+        <v>23.09954247569013</v>
       </c>
       <c r="O11" t="n">
-        <v>4.816277752464162</v>
+        <v>4.806198339195973</v>
       </c>
       <c r="P11" t="n">
-        <v>256.0568393631735</v>
+        <v>256.0534070989513</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34440,28 +34586,28 @@
         <v>0.0526</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1171286435641078</v>
+        <v>-0.1157950529425949</v>
       </c>
       <c r="J12" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K12" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02883737802839403</v>
+        <v>0.02845916890285038</v>
       </c>
       <c r="M12" t="n">
-        <v>4.066161127289131</v>
+        <v>4.05470675523467</v>
       </c>
       <c r="N12" t="n">
-        <v>25.54714045128419</v>
+        <v>25.45059876230445</v>
       </c>
       <c r="O12" t="n">
-        <v>5.054417914189941</v>
+        <v>5.04485864641463</v>
       </c>
       <c r="P12" t="n">
-        <v>255.8169819142811</v>
+        <v>255.803196094569</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34512,28 +34658,28 @@
         <v>0.0537</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2852372660409462</v>
+        <v>-0.286720061777221</v>
       </c>
       <c r="J13" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K13" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1604762769065331</v>
+        <v>0.1631445198402462</v>
       </c>
       <c r="M13" t="n">
-        <v>3.801295572876393</v>
+        <v>3.791726394658725</v>
       </c>
       <c r="N13" t="n">
-        <v>23.53501842648838</v>
+        <v>23.44624431651107</v>
       </c>
       <c r="O13" t="n">
-        <v>4.851290387771936</v>
+        <v>4.842132207665448</v>
       </c>
       <c r="P13" t="n">
-        <v>260.9579480814568</v>
+        <v>260.9732943489371</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34584,28 +34730,28 @@
         <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3458613794093807</v>
+        <v>-0.3500367330329591</v>
       </c>
       <c r="J14" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K14" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2197000868266299</v>
+        <v>0.2248251643753868</v>
       </c>
       <c r="M14" t="n">
-        <v>3.798704455653493</v>
+        <v>3.801237626155507</v>
       </c>
       <c r="N14" t="n">
-        <v>23.49174879332313</v>
+        <v>23.48881668431609</v>
       </c>
       <c r="O14" t="n">
-        <v>4.846828735711953</v>
+        <v>4.846526249213563</v>
       </c>
       <c r="P14" t="n">
-        <v>264.9004674690889</v>
+        <v>264.9436692714235</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34656,28 +34802,28 @@
         <v>0.0466</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4064546346408455</v>
+        <v>-0.4150987934275333</v>
       </c>
       <c r="J15" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K15" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1945789688763929</v>
+        <v>0.2010829463428133</v>
       </c>
       <c r="M15" t="n">
-        <v>5.05806769446791</v>
+        <v>5.086318988532578</v>
       </c>
       <c r="N15" t="n">
-        <v>37.81212697912118</v>
+        <v>38.06348443757796</v>
       </c>
       <c r="O15" t="n">
-        <v>6.149156607138997</v>
+        <v>6.169561121958187</v>
       </c>
       <c r="P15" t="n">
-        <v>267.3728074285601</v>
+        <v>267.4622371854072</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34728,28 +34874,28 @@
         <v>0.0412</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5634642300323687</v>
+        <v>-0.5716863285513619</v>
       </c>
       <c r="J16" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K16" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3040475908394714</v>
+        <v>0.3103360850064644</v>
       </c>
       <c r="M16" t="n">
-        <v>5.171815334986193</v>
+        <v>5.195069037746824</v>
       </c>
       <c r="N16" t="n">
-        <v>40.18375877830287</v>
+        <v>40.38313099720414</v>
       </c>
       <c r="O16" t="n">
-        <v>6.339066080922557</v>
+        <v>6.354772300972249</v>
       </c>
       <c r="P16" t="n">
-        <v>273.9386862609371</v>
+        <v>274.0237452871492</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34800,28 +34946,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.472237537653125</v>
+        <v>-0.4800183115546803</v>
       </c>
       <c r="J17" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K17" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2041446980497166</v>
+        <v>0.2099908082743774</v>
       </c>
       <c r="M17" t="n">
-        <v>5.384608991856134</v>
+        <v>5.396141971116755</v>
       </c>
       <c r="N17" t="n">
-        <v>48.0725212141416</v>
+        <v>48.19773369205929</v>
       </c>
       <c r="O17" t="n">
-        <v>6.933435022709999</v>
+        <v>6.942458764159805</v>
       </c>
       <c r="P17" t="n">
-        <v>277.076711886761</v>
+        <v>277.1572036403267</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34872,28 +35018,28 @@
         <v>0.0308</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2861600490570747</v>
+        <v>-0.295271092004397</v>
       </c>
       <c r="J18" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K18" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05019549903486697</v>
+        <v>0.05349861903477793</v>
       </c>
       <c r="M18" t="n">
-        <v>7.26422888771028</v>
+        <v>7.278559698843101</v>
       </c>
       <c r="N18" t="n">
-        <v>85.67760734743705</v>
+        <v>85.76294570028281</v>
       </c>
       <c r="O18" t="n">
-        <v>9.256219927564224</v>
+        <v>9.260828564458086</v>
       </c>
       <c r="P18" t="n">
-        <v>279.4124675041743</v>
+        <v>279.5067248238187</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34931,7 +35077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S453"/>
+  <dimension ref="A1:S455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78875,6 +79021,200 @@
         </is>
       </c>
     </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:18+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>-40.72986377217753,172.69704040889215</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>-40.72931520745221,172.696425625602</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-40.72869265209768,172.69591912142053</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-40.72820180458325,172.69558714380958</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>-40.72753665866581,172.69522256584372</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>-40.72689282731757,172.6948956177991</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>-40.72620727023812,172.69460345559472</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>-40.72551138049685,172.69435320327665</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>-40.72485811468318,172.694170939214</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>-40.72415811686664,172.6939428773965</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>-40.72344999987649,172.69376521115413</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>-40.72274098470495,172.69351152413864</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>-40.72204308539762,172.69328709500354</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>-40.72135014487709,172.69302211395257</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>-40.72063959677167,172.69283088228073</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>-40.71992678472287,172.69267499545026</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>-40.71921330770877,172.69252340786554</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:13:18+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>-40.729878344916294,172.69701893547443</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>-40.729330139895985,172.69640362202102</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>-40.72870597714869,172.69589951778642</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-40.72820942790682,172.69556220062415</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-40.727545821786514,172.69519256574176</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>-40.72689750736802,172.69487657457708</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-40.72621322408811,172.69457922923337</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>-40.72551813879042,172.69432571004</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>-40.7248624502358,172.69414358124777</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>-40.72416188224628,172.6939191131266</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>-40.72345432096871,172.69373797075718</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>-40.72274427303954,172.69349332176557</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>-40.72204679744761,172.6932661045314</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>-40.721353017856174,172.693005851405</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>-40.72064040339051,172.692826509601</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>-40.71992669981622,172.69267545572762</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>-40.71921513151356,172.69251351147025</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0574/nzd0574.xlsx
+++ b/data/nzd0574/nzd0574.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S455"/>
+  <dimension ref="A1:S457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29125,6 +29125,132 @@
         <v>261.09</v>
       </c>
       <c r="S455" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>234.65</v>
+      </c>
+      <c r="C456" t="n">
+        <v>236.25</v>
+      </c>
+      <c r="D456" t="n">
+        <v>250.31</v>
+      </c>
+      <c r="E456" t="n">
+        <v>245.88</v>
+      </c>
+      <c r="F456" t="n">
+        <v>245.05</v>
+      </c>
+      <c r="G456" t="n">
+        <v>245.75</v>
+      </c>
+      <c r="H456" t="n">
+        <v>246.72</v>
+      </c>
+      <c r="I456" t="n">
+        <v>250.1</v>
+      </c>
+      <c r="J456" t="n">
+        <v>254.86</v>
+      </c>
+      <c r="K456" t="n">
+        <v>252.75</v>
+      </c>
+      <c r="L456" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="M456" t="n">
+        <v>251.63</v>
+      </c>
+      <c r="N456" t="n">
+        <v>250.61</v>
+      </c>
+      <c r="O456" t="n">
+        <v>246.32</v>
+      </c>
+      <c r="P456" t="n">
+        <v>249.24</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>256.05</v>
+      </c>
+      <c r="R456" t="n">
+        <v>261.14</v>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-09 22:13:14+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>233.19</v>
+      </c>
+      <c r="C457" t="n">
+        <v>234.67</v>
+      </c>
+      <c r="D457" t="n">
+        <v>248.97</v>
+      </c>
+      <c r="E457" t="n">
+        <v>244.5</v>
+      </c>
+      <c r="F457" t="n">
+        <v>244</v>
+      </c>
+      <c r="G457" t="n">
+        <v>245.68</v>
+      </c>
+      <c r="H457" t="n">
+        <v>246.36</v>
+      </c>
+      <c r="I457" t="n">
+        <v>249.11</v>
+      </c>
+      <c r="J457" t="n">
+        <v>253.68</v>
+      </c>
+      <c r="K457" t="n">
+        <v>251.67</v>
+      </c>
+      <c r="L457" t="n">
+        <v>252.91</v>
+      </c>
+      <c r="M457" t="n">
+        <v>250.7</v>
+      </c>
+      <c r="N457" t="n">
+        <v>249.78</v>
+      </c>
+      <c r="O457" t="n">
+        <v>246.41</v>
+      </c>
+      <c r="P457" t="n">
+        <v>249.01</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>256.85</v>
+      </c>
+      <c r="R457" t="n">
+        <v>261.27</v>
+      </c>
+      <c r="S457" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29141,7 +29267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B456"/>
+  <dimension ref="A1:B458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33704,6 +33830,26 @@
       </c>
       <c r="B456" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-02-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -33866,28 +34012,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1899923472105069</v>
+        <v>0.186544802260318</v>
       </c>
       <c r="J2" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K2" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1074063983993804</v>
+        <v>0.1044753711257616</v>
       </c>
       <c r="M2" t="n">
-        <v>3.293991419382248</v>
+        <v>3.295839914478092</v>
       </c>
       <c r="N2" t="n">
-        <v>16.67919094025876</v>
+        <v>16.67548504575904</v>
       </c>
       <c r="O2" t="n">
-        <v>4.084016520566335</v>
+        <v>4.083562788271908</v>
       </c>
       <c r="P2" t="n">
-        <v>232.8203348852874</v>
+        <v>232.8560869000522</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33938,28 +34084,28 @@
         <v>0.0863</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05492667717562882</v>
+        <v>0.05322675138740062</v>
       </c>
       <c r="J3" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K3" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01053539894327293</v>
+        <v>0.00998474680584327</v>
       </c>
       <c r="M3" t="n">
-        <v>3.313488680893711</v>
+        <v>3.306676536759305</v>
       </c>
       <c r="N3" t="n">
-        <v>15.75415370463539</v>
+        <v>15.70410926685459</v>
       </c>
       <c r="O3" t="n">
-        <v>3.969150249692671</v>
+        <v>3.962841060004121</v>
       </c>
       <c r="P3" t="n">
-        <v>235.9471161001999</v>
+        <v>235.9647466628426</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34010,28 +34156,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01290013029533877</v>
+        <v>0.01297273398947955</v>
       </c>
       <c r="J4" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K4" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005527104638958225</v>
+        <v>0.0005644086057585707</v>
       </c>
       <c r="M4" t="n">
-        <v>3.41399631900316</v>
+        <v>3.401966775678212</v>
       </c>
       <c r="N4" t="n">
-        <v>16.73129475044498</v>
+        <v>16.65991448724602</v>
       </c>
       <c r="O4" t="n">
-        <v>4.090390537643683</v>
+        <v>4.081655851152326</v>
       </c>
       <c r="P4" t="n">
-        <v>249.2163352967679</v>
+        <v>249.2155853303104</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34082,28 +34228,28 @@
         <v>0.0901</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02097163609778561</v>
+        <v>-0.02204718270872046</v>
       </c>
       <c r="J5" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K5" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001481318796738518</v>
+        <v>0.001652215248667765</v>
       </c>
       <c r="M5" t="n">
-        <v>3.287221186597892</v>
+        <v>3.277974752543644</v>
       </c>
       <c r="N5" t="n">
-        <v>16.48357603460979</v>
+        <v>16.41988053183556</v>
       </c>
       <c r="O5" t="n">
-        <v>4.059997048596191</v>
+        <v>4.05214517654977</v>
       </c>
       <c r="P5" t="n">
-        <v>246.9749366034419</v>
+        <v>246.9860923033974</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34154,28 +34300,28 @@
         <v>0.0813</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07980540040280369</v>
+        <v>-0.08003033395288099</v>
       </c>
       <c r="J6" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K6" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02001491611606532</v>
+        <v>0.02031909772334062</v>
       </c>
       <c r="M6" t="n">
-        <v>3.377989388324098</v>
+        <v>3.365440325730679</v>
       </c>
       <c r="N6" t="n">
-        <v>17.33841531485085</v>
+        <v>17.26386532021733</v>
       </c>
       <c r="O6" t="n">
-        <v>4.163942280441799</v>
+        <v>4.154980784578592</v>
       </c>
       <c r="P6" t="n">
-        <v>246.8978285699023</v>
+        <v>246.9001632513798</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34226,28 +34372,28 @@
         <v>0.0902</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1535656602889079</v>
+        <v>-0.1529466311646491</v>
       </c>
       <c r="J7" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K7" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0639363658104275</v>
+        <v>0.06403575937291239</v>
       </c>
       <c r="M7" t="n">
-        <v>3.441471794371116</v>
+        <v>3.429299161914903</v>
       </c>
       <c r="N7" t="n">
-        <v>19.19662131641995</v>
+        <v>19.11459416134942</v>
       </c>
       <c r="O7" t="n">
-        <v>4.381394905326379</v>
+        <v>4.372024034854957</v>
       </c>
       <c r="P7" t="n">
-        <v>249.085632984768</v>
+        <v>249.0792141823217</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34298,28 +34444,28 @@
         <v>0.0733</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1900787238127319</v>
+        <v>-0.190246526388895</v>
       </c>
       <c r="J8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1180767132758598</v>
+        <v>0.1192896519245827</v>
       </c>
       <c r="M8" t="n">
-        <v>3.059640070142374</v>
+        <v>3.046996703795689</v>
       </c>
       <c r="N8" t="n">
-        <v>15.00419562247538</v>
+        <v>14.93868458832432</v>
       </c>
       <c r="O8" t="n">
-        <v>3.873524960869025</v>
+        <v>3.865059454694626</v>
       </c>
       <c r="P8" t="n">
-        <v>251.7758299174149</v>
+        <v>251.7775706881161</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34370,28 +34516,28 @@
         <v>0.0664</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2222969318392278</v>
+        <v>-0.2225769748483883</v>
       </c>
       <c r="J9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1197764337908488</v>
+        <v>0.1210787082583796</v>
       </c>
       <c r="M9" t="n">
-        <v>3.574232495707349</v>
+        <v>3.56061112840321</v>
       </c>
       <c r="N9" t="n">
-        <v>20.19145889581563</v>
+        <v>20.1044054951282</v>
       </c>
       <c r="O9" t="n">
-        <v>4.493490725017202</v>
+        <v>4.48379364992728</v>
       </c>
       <c r="P9" t="n">
-        <v>255.8196151227124</v>
+        <v>255.8225211126003</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34442,28 +34588,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1508402753753969</v>
+        <v>-0.1497208251041698</v>
       </c>
       <c r="J10" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K10" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05180900551871004</v>
+        <v>0.05154343479370649</v>
       </c>
       <c r="M10" t="n">
-        <v>3.726652761598036</v>
+        <v>3.715542037496635</v>
       </c>
       <c r="N10" t="n">
-        <v>23.15284434450932</v>
+        <v>23.05988157729997</v>
       </c>
       <c r="O10" t="n">
-        <v>4.811740261538367</v>
+        <v>4.80207055105399</v>
       </c>
       <c r="P10" t="n">
-        <v>256.9931672155395</v>
+        <v>256.981561745031</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34514,28 +34660,28 @@
         <v>0.0576</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1281179639914296</v>
+        <v>-0.1285059450570938</v>
       </c>
       <c r="J11" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K11" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03800734924334381</v>
+        <v>0.03858955165125399</v>
       </c>
       <c r="M11" t="n">
-        <v>3.703802895340449</v>
+        <v>3.689939983689543</v>
       </c>
       <c r="N11" t="n">
-        <v>23.09954247569013</v>
+        <v>23.00033187368724</v>
       </c>
       <c r="O11" t="n">
-        <v>4.806198339195973</v>
+        <v>4.795866123411624</v>
       </c>
       <c r="P11" t="n">
-        <v>256.0534070989513</v>
+        <v>256.0574325207116</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34586,28 +34732,28 @@
         <v>0.0526</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1157950529425949</v>
+        <v>-0.1153817220274306</v>
       </c>
       <c r="J12" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K12" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02845916890285038</v>
+        <v>0.02853244294139201</v>
       </c>
       <c r="M12" t="n">
-        <v>4.05470675523467</v>
+        <v>4.038904013915448</v>
       </c>
       <c r="N12" t="n">
-        <v>25.45059876230445</v>
+        <v>25.34031066013459</v>
       </c>
       <c r="O12" t="n">
-        <v>5.04485864641463</v>
+        <v>5.033916036261887</v>
       </c>
       <c r="P12" t="n">
-        <v>255.803196094569</v>
+        <v>255.7989113678881</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34658,28 +34804,28 @@
         <v>0.0537</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.286720061777221</v>
+        <v>-0.288648051526975</v>
       </c>
       <c r="J13" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K13" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1631445198402462</v>
+        <v>0.166214259434736</v>
       </c>
       <c r="M13" t="n">
-        <v>3.791726394658725</v>
+        <v>3.784348145732911</v>
       </c>
       <c r="N13" t="n">
-        <v>23.44624431651107</v>
+        <v>23.36533451171225</v>
       </c>
       <c r="O13" t="n">
-        <v>4.842132207665448</v>
+        <v>4.833770217098889</v>
       </c>
       <c r="P13" t="n">
-        <v>260.9732943489371</v>
+        <v>260.9932883786637</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34730,28 +34876,28 @@
         <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3500367330329591</v>
+        <v>-0.3548159720026011</v>
       </c>
       <c r="J14" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K14" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2248251643753868</v>
+        <v>0.230352362492382</v>
       </c>
       <c r="M14" t="n">
-        <v>3.801237626155507</v>
+        <v>3.806682936896607</v>
       </c>
       <c r="N14" t="n">
-        <v>23.48881668431609</v>
+        <v>23.515496379263</v>
       </c>
       <c r="O14" t="n">
-        <v>4.846526249213563</v>
+        <v>4.849277923491599</v>
       </c>
       <c r="P14" t="n">
-        <v>264.9436692714235</v>
+        <v>264.9932287201314</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34802,28 +34948,28 @@
         <v>0.0466</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4150987934275333</v>
+        <v>-0.4239194528850027</v>
       </c>
       <c r="J15" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K15" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2010829463428133</v>
+        <v>0.2076479684713437</v>
       </c>
       <c r="M15" t="n">
-        <v>5.086318988532578</v>
+        <v>5.115739034311302</v>
       </c>
       <c r="N15" t="n">
-        <v>38.06348443757796</v>
+        <v>38.33590668468239</v>
       </c>
       <c r="O15" t="n">
-        <v>6.169561121958187</v>
+        <v>6.191599687050382</v>
       </c>
       <c r="P15" t="n">
-        <v>267.4622371854072</v>
+        <v>267.5537016274387</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34874,28 +35020,28 @@
         <v>0.0412</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5716863285513619</v>
+        <v>-0.5802005038847032</v>
       </c>
       <c r="J16" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K16" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3103360850064644</v>
+        <v>0.316638885619718</v>
       </c>
       <c r="M16" t="n">
-        <v>5.195069037746824</v>
+        <v>5.219737158871578</v>
       </c>
       <c r="N16" t="n">
-        <v>40.38313099720414</v>
+        <v>40.61540378266195</v>
       </c>
       <c r="O16" t="n">
-        <v>6.354772300972249</v>
+        <v>6.373021558308269</v>
       </c>
       <c r="P16" t="n">
-        <v>274.0237452871492</v>
+        <v>274.1120323508183</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34946,28 +35092,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4800183115546803</v>
+        <v>-0.4869895572414338</v>
       </c>
       <c r="J17" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K17" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2099908082743774</v>
+        <v>0.215512681946805</v>
       </c>
       <c r="M17" t="n">
-        <v>5.396141971116755</v>
+        <v>5.404074891947467</v>
       </c>
       <c r="N17" t="n">
-        <v>48.19773369205929</v>
+        <v>48.26151498084439</v>
       </c>
       <c r="O17" t="n">
-        <v>6.942458764159805</v>
+        <v>6.947050811736185</v>
       </c>
       <c r="P17" t="n">
-        <v>277.1572036403267</v>
+        <v>277.2294893026925</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35018,28 +35164,28 @@
         <v>0.0308</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.295271092004397</v>
+        <v>-0.3044326554328805</v>
       </c>
       <c r="J18" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K18" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05349861903477793</v>
+        <v>0.05691008825931743</v>
       </c>
       <c r="M18" t="n">
-        <v>7.278559698843101</v>
+        <v>7.293742834013473</v>
       </c>
       <c r="N18" t="n">
-        <v>85.76294570028281</v>
+        <v>85.86078796892036</v>
       </c>
       <c r="O18" t="n">
-        <v>9.260828564458086</v>
+        <v>9.266109645850321</v>
       </c>
       <c r="P18" t="n">
-        <v>279.5067248238187</v>
+        <v>279.6017241436959</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35077,7 +35223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S455"/>
+  <dimension ref="A1:S457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79215,6 +79361,200 @@
         </is>
       </c>
     </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>-40.729880203989666,172.69701619606656</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>-40.72933295846924,172.69639946873355</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>-40.72871071894531,172.69589254171655</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-40.7282131891922,172.69554989385216</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>-40.727547298625765,172.69518773055972</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>-40.72690052586044,172.6948642922609</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>-40.726212061010834,172.69458396182523</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>-40.72551689238432,172.6943307805144</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>-40.72486217467121,172.69414532010168</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>-40.72416052303664,172.69392769144872</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>-40.72345349352602,172.6937431870037</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>-40.72274283699503,172.6935012709034</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>-40.722045777654046,172.69327187114484</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>-40.72135261034154,172.6930081581494</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>-40.72064099774114,172.69282328762637</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>-40.7199261266962,172.69267856259972</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>-40.71921502547843,172.6925140868421</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-09 22:13:14+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>-40.72988895962467,172.6970032943371</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>-40.72934243367181,172.69638550661566</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>-40.72871876199176,172.69588070888685</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-40.728217823631326,172.69553473014903</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-40.72755082290039,172.6951761920563</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>-40.726900719708524,172.69486350348825</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>-40.726213057934224,172.69457990531797</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>-40.72551963447747,172.6943196254705</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>-40.724864342445294,172.69413164111737</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>-40.72416250674779,172.69391517173523</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>-40.72345457839528,172.6937363479249</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>-40.722744772533154,172.693490556848</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>-40.72204747051122,172.69326229856642</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>-40.72135242695995,172.6930091961844</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>-40.72064148595765,172.69282064100432</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>-40.71992442856231,172.69268776814633</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>-40.71921474978704,172.69251558280885</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0574/nzd0574.xlsx
+++ b/data/nzd0574/nzd0574.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S457"/>
+  <dimension ref="A1:S460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29251,6 +29251,195 @@
         <v>261.27</v>
       </c>
       <c r="S457" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:13:02+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>233.34</v>
+      </c>
+      <c r="C458" t="n">
+        <v>234.75</v>
+      </c>
+      <c r="D458" t="n">
+        <v>248.43</v>
+      </c>
+      <c r="E458" t="n">
+        <v>244.02</v>
+      </c>
+      <c r="F458" t="n">
+        <v>243.74</v>
+      </c>
+      <c r="G458" t="n">
+        <v>244.96</v>
+      </c>
+      <c r="H458" t="n">
+        <v>246.53</v>
+      </c>
+      <c r="I458" t="n">
+        <v>249.4</v>
+      </c>
+      <c r="J458" t="n">
+        <v>253.47</v>
+      </c>
+      <c r="K458" t="n">
+        <v>252.24</v>
+      </c>
+      <c r="L458" t="n">
+        <v>253.08</v>
+      </c>
+      <c r="M458" t="n">
+        <v>251.04</v>
+      </c>
+      <c r="N458" t="n">
+        <v>250.15</v>
+      </c>
+      <c r="O458" t="n">
+        <v>246.57</v>
+      </c>
+      <c r="P458" t="n">
+        <v>249.05</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>256.9</v>
+      </c>
+      <c r="R458" t="n">
+        <v>261.16</v>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>231.83</v>
+      </c>
+      <c r="C459" t="n">
+        <v>233.85</v>
+      </c>
+      <c r="D459" t="n">
+        <v>247.24</v>
+      </c>
+      <c r="E459" t="n">
+        <v>242.82</v>
+      </c>
+      <c r="F459" t="n">
+        <v>242.95</v>
+      </c>
+      <c r="G459" t="n">
+        <v>243.84</v>
+      </c>
+      <c r="H459" t="n">
+        <v>246.12</v>
+      </c>
+      <c r="I459" t="n">
+        <v>249.23</v>
+      </c>
+      <c r="J459" t="n">
+        <v>252.69</v>
+      </c>
+      <c r="K459" t="n">
+        <v>252.11</v>
+      </c>
+      <c r="L459" t="n">
+        <v>252.54</v>
+      </c>
+      <c r="M459" t="n">
+        <v>250.62</v>
+      </c>
+      <c r="N459" t="n">
+        <v>248.73</v>
+      </c>
+      <c r="O459" t="n">
+        <v>246.38</v>
+      </c>
+      <c r="P459" t="n">
+        <v>247.71</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>255.18</v>
+      </c>
+      <c r="R459" t="n">
+        <v>259.01</v>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>232.22</v>
+      </c>
+      <c r="C460" t="n">
+        <v>233.98</v>
+      </c>
+      <c r="D460" t="n">
+        <v>247.2</v>
+      </c>
+      <c r="E460" t="n">
+        <v>242.76</v>
+      </c>
+      <c r="F460" t="n">
+        <v>242.8</v>
+      </c>
+      <c r="G460" t="n">
+        <v>243.84</v>
+      </c>
+      <c r="H460" t="n">
+        <v>246.67</v>
+      </c>
+      <c r="I460" t="n">
+        <v>249.55</v>
+      </c>
+      <c r="J460" t="n">
+        <v>253.36</v>
+      </c>
+      <c r="K460" t="n">
+        <v>252.67</v>
+      </c>
+      <c r="L460" t="n">
+        <v>253.97</v>
+      </c>
+      <c r="M460" t="n">
+        <v>251.33</v>
+      </c>
+      <c r="N460" t="n">
+        <v>249.83</v>
+      </c>
+      <c r="O460" t="n">
+        <v>246.97</v>
+      </c>
+      <c r="P460" t="n">
+        <v>248.16</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>256.12</v>
+      </c>
+      <c r="R460" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="S460" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29267,7 +29456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B458"/>
+  <dimension ref="A1:B461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33850,6 +34039,36 @@
       </c>
       <c r="B458" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -34012,28 +34231,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.186544802260318</v>
+        <v>0.179614460128573</v>
       </c>
       <c r="J2" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K2" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1044753711257616</v>
+        <v>0.09790274561202628</v>
       </c>
       <c r="M2" t="n">
-        <v>3.295839914478092</v>
+        <v>3.306623349550961</v>
       </c>
       <c r="N2" t="n">
-        <v>16.67548504575904</v>
+        <v>16.75292054153565</v>
       </c>
       <c r="O2" t="n">
-        <v>4.083562788271908</v>
+        <v>4.093033171321196</v>
       </c>
       <c r="P2" t="n">
-        <v>232.8560869000522</v>
+        <v>232.9281734448705</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34084,28 +34303,28 @@
         <v>0.0863</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05322675138740062</v>
+        <v>0.04910248742328383</v>
       </c>
       <c r="J3" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K3" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00998474680584327</v>
+        <v>0.008598143705000227</v>
       </c>
       <c r="M3" t="n">
-        <v>3.306676536759305</v>
+        <v>3.303621172842753</v>
       </c>
       <c r="N3" t="n">
-        <v>15.70410926685459</v>
+        <v>15.66756333764611</v>
       </c>
       <c r="O3" t="n">
-        <v>3.962841060004121</v>
+        <v>3.958227297370138</v>
       </c>
       <c r="P3" t="n">
-        <v>235.9647466628426</v>
+        <v>236.0076461313068</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34156,28 +34375,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01297273398947955</v>
+        <v>0.01046366036681173</v>
       </c>
       <c r="J4" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K4" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005644086057585707</v>
+        <v>0.00037208641844233</v>
       </c>
       <c r="M4" t="n">
-        <v>3.401966775678212</v>
+        <v>3.392036408937878</v>
       </c>
       <c r="N4" t="n">
-        <v>16.65991448724602</v>
+        <v>16.57720357359687</v>
       </c>
       <c r="O4" t="n">
-        <v>4.081655851152326</v>
+        <v>4.071511214966362</v>
       </c>
       <c r="P4" t="n">
-        <v>249.2155853303104</v>
+        <v>249.2416892448728</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34228,28 +34447,28 @@
         <v>0.0901</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02204718270872046</v>
+        <v>-0.02618514206705283</v>
       </c>
       <c r="J5" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K5" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001652215248667765</v>
+        <v>0.002353506954506424</v>
       </c>
       <c r="M5" t="n">
-        <v>3.277974752543644</v>
+        <v>3.276327996426503</v>
       </c>
       <c r="N5" t="n">
-        <v>16.41988053183556</v>
+        <v>16.38024932350099</v>
       </c>
       <c r="O5" t="n">
-        <v>4.05214517654977</v>
+        <v>4.047252070664859</v>
       </c>
       <c r="P5" t="n">
-        <v>246.9860923033974</v>
+        <v>247.0291374142286</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34300,28 +34519,28 @@
         <v>0.0813</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08003033395288099</v>
+        <v>-0.08211280229235346</v>
       </c>
       <c r="J6" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K6" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02031909772334062</v>
+        <v>0.02165340099680035</v>
       </c>
       <c r="M6" t="n">
-        <v>3.365440325730679</v>
+        <v>3.353440732185694</v>
       </c>
       <c r="N6" t="n">
-        <v>17.26386532021733</v>
+        <v>17.1687158527401</v>
       </c>
       <c r="O6" t="n">
-        <v>4.154980784578592</v>
+        <v>4.1435149152308</v>
       </c>
       <c r="P6" t="n">
-        <v>246.9001632513798</v>
+        <v>246.9218281216612</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34372,28 +34591,28 @@
         <v>0.0902</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1529466311646491</v>
+        <v>-0.1539746162101207</v>
       </c>
       <c r="J7" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K7" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06403575937291239</v>
+        <v>0.06571674384896431</v>
       </c>
       <c r="M7" t="n">
-        <v>3.429299161914903</v>
+        <v>3.412262534831134</v>
       </c>
       <c r="N7" t="n">
-        <v>19.11459416134942</v>
+        <v>18.99547832574781</v>
       </c>
       <c r="O7" t="n">
-        <v>4.372024034854957</v>
+        <v>4.358380241069819</v>
       </c>
       <c r="P7" t="n">
-        <v>249.0792141823217</v>
+        <v>249.0899134756284</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34444,28 +34663,28 @@
         <v>0.0733</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.190246526388895</v>
+        <v>-0.1906001000887868</v>
       </c>
       <c r="J8" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K8" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1192896519245827</v>
+        <v>0.121223077648993</v>
       </c>
       <c r="M8" t="n">
-        <v>3.046996703795689</v>
+        <v>3.028697582623395</v>
       </c>
       <c r="N8" t="n">
-        <v>14.93868458832432</v>
+        <v>14.84188392781811</v>
       </c>
       <c r="O8" t="n">
-        <v>3.865059454694626</v>
+        <v>3.852516570738938</v>
       </c>
       <c r="P8" t="n">
-        <v>251.7775706881161</v>
+        <v>251.7812476729097</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34516,28 +34735,28 @@
         <v>0.0664</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2225769748483883</v>
+        <v>-0.2232332150080203</v>
       </c>
       <c r="J9" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K9" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1210787082583796</v>
+        <v>0.123268478000008</v>
       </c>
       <c r="M9" t="n">
-        <v>3.56061112840321</v>
+        <v>3.540342799998064</v>
       </c>
       <c r="N9" t="n">
-        <v>20.1044054951282</v>
+        <v>19.97476415803583</v>
       </c>
       <c r="O9" t="n">
-        <v>4.48379364992728</v>
+        <v>4.469313611510813</v>
       </c>
       <c r="P9" t="n">
-        <v>255.8225211126003</v>
+        <v>255.8293455357806</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34588,28 +34807,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1497208251041698</v>
+        <v>-0.1494958602200075</v>
       </c>
       <c r="J10" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K10" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05154343479370649</v>
+        <v>0.05211193143658399</v>
       </c>
       <c r="M10" t="n">
-        <v>3.715542037496635</v>
+        <v>3.693667349761224</v>
       </c>
       <c r="N10" t="n">
-        <v>23.05988157729997</v>
+        <v>22.91013585148195</v>
       </c>
       <c r="O10" t="n">
-        <v>4.80207055105399</v>
+        <v>4.78645336877755</v>
       </c>
       <c r="P10" t="n">
-        <v>256.981561745031</v>
+        <v>256.9792236636596</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34660,28 +34879,28 @@
         <v>0.0576</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1285059450570938</v>
+        <v>-0.1288946065475998</v>
       </c>
       <c r="J11" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K11" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03858955165125399</v>
+        <v>0.03936173546292943</v>
       </c>
       <c r="M11" t="n">
-        <v>3.689939983689543</v>
+        <v>3.667960556485671</v>
       </c>
       <c r="N11" t="n">
-        <v>23.00033187368724</v>
+        <v>22.85096674437265</v>
       </c>
       <c r="O11" t="n">
-        <v>4.795866123411624</v>
+        <v>4.780268480365161</v>
       </c>
       <c r="P11" t="n">
-        <v>256.0574325207116</v>
+        <v>256.0614724012875</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34732,28 +34951,28 @@
         <v>0.0526</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1153817220274306</v>
+        <v>-0.1147760369404733</v>
       </c>
       <c r="J12" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K12" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02853244294139201</v>
+        <v>0.02864202513143177</v>
       </c>
       <c r="M12" t="n">
-        <v>4.038904013915448</v>
+        <v>4.016221193596678</v>
       </c>
       <c r="N12" t="n">
-        <v>25.34031066013459</v>
+        <v>25.17836258345065</v>
       </c>
       <c r="O12" t="n">
-        <v>5.033916036261887</v>
+        <v>5.017804558116094</v>
       </c>
       <c r="P12" t="n">
-        <v>255.7989113678881</v>
+        <v>255.7926076793984</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34804,28 +35023,28 @@
         <v>0.0537</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.288648051526975</v>
+        <v>-0.2916433576733292</v>
       </c>
       <c r="J13" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K13" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L13" t="n">
-        <v>0.166214259434736</v>
+        <v>0.1709462687199077</v>
       </c>
       <c r="M13" t="n">
-        <v>3.784348145732911</v>
+        <v>3.774007355533559</v>
       </c>
       <c r="N13" t="n">
-        <v>23.36533451171225</v>
+        <v>23.24752247392559</v>
       </c>
       <c r="O13" t="n">
-        <v>4.833770217098889</v>
+        <v>4.82156846616592</v>
       </c>
       <c r="P13" t="n">
-        <v>260.9932883786637</v>
+        <v>261.0244393923091</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34876,28 +35095,28 @@
         <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3548159720026011</v>
+        <v>-0.3625513888450382</v>
       </c>
       <c r="J14" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K14" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L14" t="n">
-        <v>0.230352362492382</v>
+        <v>0.2389538095991685</v>
       </c>
       <c r="M14" t="n">
-        <v>3.806682936896607</v>
+        <v>3.817693859193795</v>
       </c>
       <c r="N14" t="n">
-        <v>23.515496379263</v>
+        <v>23.59313476405231</v>
       </c>
       <c r="O14" t="n">
-        <v>4.849277923491599</v>
+        <v>4.857276475974197</v>
       </c>
       <c r="P14" t="n">
-        <v>264.9932287201314</v>
+        <v>265.073683384487</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34948,28 +35167,28 @@
         <v>0.0466</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4239194528850027</v>
+        <v>-0.4363771052678012</v>
       </c>
       <c r="J15" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K15" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2076479684713437</v>
+        <v>0.2171924430955486</v>
       </c>
       <c r="M15" t="n">
-        <v>5.115739034311302</v>
+        <v>5.156130862895071</v>
       </c>
       <c r="N15" t="n">
-        <v>38.33590668468239</v>
+        <v>38.67974993168106</v>
       </c>
       <c r="O15" t="n">
-        <v>6.191599687050382</v>
+        <v>6.219304618016475</v>
       </c>
       <c r="P15" t="n">
-        <v>267.5537016274387</v>
+        <v>267.6832632773559</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35020,28 +35239,28 @@
         <v>0.0412</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5802005038847032</v>
+        <v>-0.5936098290390943</v>
       </c>
       <c r="J16" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K16" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L16" t="n">
-        <v>0.316638885619718</v>
+        <v>0.3260948238240189</v>
       </c>
       <c r="M16" t="n">
-        <v>5.219737158871578</v>
+        <v>5.26205490542104</v>
       </c>
       <c r="N16" t="n">
-        <v>40.61540378266195</v>
+        <v>41.03991932098051</v>
       </c>
       <c r="O16" t="n">
-        <v>6.373021558308269</v>
+        <v>6.406240654313613</v>
       </c>
       <c r="P16" t="n">
-        <v>274.1120323508183</v>
+        <v>274.2515006900201</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35092,28 +35311,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4869895572414338</v>
+        <v>-0.4976062134444443</v>
       </c>
       <c r="J17" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K17" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L17" t="n">
-        <v>0.215512681946805</v>
+        <v>0.22386576220417</v>
       </c>
       <c r="M17" t="n">
-        <v>5.404074891947467</v>
+        <v>5.416658994499208</v>
       </c>
       <c r="N17" t="n">
-        <v>48.26151498084439</v>
+        <v>48.38048276704386</v>
       </c>
       <c r="O17" t="n">
-        <v>6.947050811736185</v>
+        <v>6.955608008437785</v>
       </c>
       <c r="P17" t="n">
-        <v>277.2294893026925</v>
+        <v>277.3399128581967</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35164,28 +35383,28 @@
         <v>0.0308</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3044326554328805</v>
+        <v>-0.3193286257563056</v>
       </c>
       <c r="J18" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K18" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05691008825931743</v>
+        <v>0.06253273006758986</v>
       </c>
       <c r="M18" t="n">
-        <v>7.293742834013473</v>
+        <v>7.323690858305167</v>
       </c>
       <c r="N18" t="n">
-        <v>85.86078796892036</v>
+        <v>86.15368796674451</v>
       </c>
       <c r="O18" t="n">
-        <v>9.266109645850321</v>
+        <v>9.281901096582775</v>
       </c>
       <c r="P18" t="n">
-        <v>279.6017241436959</v>
+        <v>279.7566581669277</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35223,7 +35442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S457"/>
+  <dimension ref="A1:S460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79555,6 +79774,297 @@
         </is>
       </c>
     </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:13:02+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>-40.7298880600732,172.69700461985738</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>-40.72934195391476,172.6963862135584</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>-40.72872200321906,172.6958759404323</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-40.72821943560968,172.69552945581705</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>-40.72755169557773,172.69517333490285</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>-40.72690271357429,172.694855390398</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>-40.726212587164866,172.69458182089085</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>-40.72551883123817,172.69432289310973</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>-40.72486472823542,172.69412920672175</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>-40.72416145978928,172.6939217793619</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>-40.72345426580588,172.69373831850695</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>-40.72274406491719,172.69349447381455</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>-40.72204671586413,172.69326656586048</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>-40.7213521009482,172.6930110415799</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>-40.720641401050436,172.69282110128643</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>-40.71992432242892,172.69268834349296</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>-40.71921498306437,172.6925143169908</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>-40.729897115557335,172.69699127628468</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>-40.729347351181325,172.69637826045167</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-40.728729145923005,172.6958654321697</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-40.72822346555451,172.69551626998592</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-40.72755434717385,172.69516465355164</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>-40.72690581514213,172.69484277003446</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-40.72621372254973,172.6945772009797</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>-40.72551930210259,172.69432097759707</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>-40.72486616116975,172.6941201646807</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>-40.724161698569326,172.69392027235932</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>-40.723455258736806,172.69373205901098</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>-40.72274493903101,172.69348963520878</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>-40.72204961207637,172.69325018867735</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>-40.721352488087156,172.69300885017273</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>-40.72064424544116,172.69280568183552</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>-40.71992797341596,172.69266855156724</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>-40.71921954257278,172.69248957600038</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>-40.72989477672383,172.69699472263824</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>-40.729346571576194,172.6963794092338</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>-40.72872938601389,172.69586507895076</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-40.728223667051715,172.69551561069434</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-40.72755485064139,172.69516300519373</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>-40.72690581514213,172.69484277003446</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>-40.72621219947242,172.69458339842146</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>-40.72551841576953,172.6943245832679</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>-40.724864930315945,172.69412793156212</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>-40.724160669978254,172.69392676406255</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>-40.72345262930785,172.6937486350832</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>-40.72274346136228,172.69349781475654</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>-40.72204736853188,172.6932628752278</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>-40.72135128591869,172.6930156550686</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>-40.72064329023556,172.69281086000947</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>-40.71992597810952,172.69267936808507</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>-40.719217909633166,172.69249843672756</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0574/nzd0574.xlsx
+++ b/data/nzd0574/nzd0574.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S460"/>
+  <dimension ref="A1:S463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29440,6 +29440,195 @@
         <v>259.78</v>
       </c>
       <c r="S460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="C461" t="n">
+        <v>234.33</v>
+      </c>
+      <c r="D461" t="n">
+        <v>247.53</v>
+      </c>
+      <c r="E461" t="n">
+        <v>242.79</v>
+      </c>
+      <c r="F461" t="n">
+        <v>243.24</v>
+      </c>
+      <c r="G461" t="n">
+        <v>244.35</v>
+      </c>
+      <c r="H461" t="n">
+        <v>246.85</v>
+      </c>
+      <c r="I461" t="n">
+        <v>249.68</v>
+      </c>
+      <c r="J461" t="n">
+        <v>254.16</v>
+      </c>
+      <c r="K461" t="n">
+        <v>252.78</v>
+      </c>
+      <c r="L461" t="n">
+        <v>254.74</v>
+      </c>
+      <c r="M461" t="n">
+        <v>251.67</v>
+      </c>
+      <c r="N461" t="n">
+        <v>249.96</v>
+      </c>
+      <c r="O461" t="n">
+        <v>247.64</v>
+      </c>
+      <c r="P461" t="n">
+        <v>248.37</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>255.19</v>
+      </c>
+      <c r="R461" t="n">
+        <v>259.21</v>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>232.88</v>
+      </c>
+      <c r="C462" t="n">
+        <v>234.43</v>
+      </c>
+      <c r="D462" t="n">
+        <v>247.17</v>
+      </c>
+      <c r="E462" t="n">
+        <v>242.61</v>
+      </c>
+      <c r="F462" t="n">
+        <v>242.96</v>
+      </c>
+      <c r="G462" t="n">
+        <v>244.35</v>
+      </c>
+      <c r="H462" t="n">
+        <v>246.56</v>
+      </c>
+      <c r="I462" t="n">
+        <v>248.7</v>
+      </c>
+      <c r="J462" t="n">
+        <v>254.08</v>
+      </c>
+      <c r="K462" t="n">
+        <v>252.02</v>
+      </c>
+      <c r="L462" t="n">
+        <v>254.59</v>
+      </c>
+      <c r="M462" t="n">
+        <v>251.25</v>
+      </c>
+      <c r="N462" t="n">
+        <v>250.25</v>
+      </c>
+      <c r="O462" t="n">
+        <v>248.16</v>
+      </c>
+      <c r="P462" t="n">
+        <v>249.21</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>255.64</v>
+      </c>
+      <c r="R462" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>232.86</v>
+      </c>
+      <c r="C463" t="n">
+        <v>234.1</v>
+      </c>
+      <c r="D463" t="n">
+        <v>246.49</v>
+      </c>
+      <c r="E463" t="n">
+        <v>242.16</v>
+      </c>
+      <c r="F463" t="n">
+        <v>242.28</v>
+      </c>
+      <c r="G463" t="n">
+        <v>243.93</v>
+      </c>
+      <c r="H463" t="n">
+        <v>246.22</v>
+      </c>
+      <c r="I463" t="n">
+        <v>247.64</v>
+      </c>
+      <c r="J463" t="n">
+        <v>253.79</v>
+      </c>
+      <c r="K463" t="n">
+        <v>251.61</v>
+      </c>
+      <c r="L463" t="n">
+        <v>254.55</v>
+      </c>
+      <c r="M463" t="n">
+        <v>251.39</v>
+      </c>
+      <c r="N463" t="n">
+        <v>250.55</v>
+      </c>
+      <c r="O463" t="n">
+        <v>248.92</v>
+      </c>
+      <c r="P463" t="n">
+        <v>249.74</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>256.25</v>
+      </c>
+      <c r="R463" t="n">
+        <v>258.51</v>
+      </c>
+      <c r="S463" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29456,7 +29645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B461"/>
+  <dimension ref="A1:B464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34069,6 +34258,36 @@
       </c>
       <c r="B461" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -34231,28 +34450,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.179614460128573</v>
+        <v>0.1733167073608332</v>
       </c>
       <c r="J2" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K2" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09790274561202628</v>
+        <v>0.09220662335965768</v>
       </c>
       <c r="M2" t="n">
-        <v>3.306623349550961</v>
+        <v>3.314340069123434</v>
       </c>
       <c r="N2" t="n">
-        <v>16.75292054153565</v>
+        <v>16.79929792655795</v>
       </c>
       <c r="O2" t="n">
-        <v>4.093033171321196</v>
+        <v>4.098694661298637</v>
       </c>
       <c r="P2" t="n">
-        <v>232.9281734448705</v>
+        <v>232.9938985156181</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34303,28 +34522,28 @@
         <v>0.0863</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04910248742328383</v>
+        <v>0.04523750060248707</v>
       </c>
       <c r="J3" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K3" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008598143705000227</v>
+        <v>0.007385192402737384</v>
       </c>
       <c r="M3" t="n">
-        <v>3.303621172842753</v>
+        <v>3.299461648832975</v>
       </c>
       <c r="N3" t="n">
-        <v>15.66756333764611</v>
+        <v>15.62433421571639</v>
       </c>
       <c r="O3" t="n">
-        <v>3.958227297370138</v>
+        <v>3.95276285852268</v>
       </c>
       <c r="P3" t="n">
-        <v>236.0076461313068</v>
+        <v>236.0479847944795</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34375,28 +34594,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01046366036681173</v>
+        <v>0.007329706020677251</v>
       </c>
       <c r="J4" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K4" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00037208641844233</v>
+        <v>0.0001848219566994436</v>
       </c>
       <c r="M4" t="n">
-        <v>3.392036408937878</v>
+        <v>3.385237514547858</v>
       </c>
       <c r="N4" t="n">
-        <v>16.57720357359687</v>
+        <v>16.50914779199273</v>
       </c>
       <c r="O4" t="n">
-        <v>4.071511214966362</v>
+        <v>4.063145061647778</v>
       </c>
       <c r="P4" t="n">
-        <v>249.2416892448728</v>
+        <v>249.2744036353057</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34447,28 +34666,28 @@
         <v>0.0901</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02618514206705283</v>
+        <v>-0.03104463807878012</v>
       </c>
       <c r="J5" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K5" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002353506954506424</v>
+        <v>0.003333873261269882</v>
       </c>
       <c r="M5" t="n">
-        <v>3.276327996426503</v>
+        <v>3.278209692349306</v>
       </c>
       <c r="N5" t="n">
-        <v>16.38024932350099</v>
+        <v>16.36662741525729</v>
       </c>
       <c r="O5" t="n">
-        <v>4.047252070664859</v>
+        <v>4.045568861761877</v>
       </c>
       <c r="P5" t="n">
-        <v>247.0291374142286</v>
+        <v>247.0798577141898</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34519,28 +34738,28 @@
         <v>0.0813</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08211280229235346</v>
+        <v>-0.08453919113624651</v>
       </c>
       <c r="J6" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K6" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02165340099680035</v>
+        <v>0.0232156152014229</v>
       </c>
       <c r="M6" t="n">
-        <v>3.353440732185694</v>
+        <v>3.343262560306308</v>
       </c>
       <c r="N6" t="n">
-        <v>17.1687158527401</v>
+        <v>17.08126651829651</v>
       </c>
       <c r="O6" t="n">
-        <v>4.1435149152308</v>
+        <v>4.132948888904449</v>
       </c>
       <c r="P6" t="n">
-        <v>246.9218281216612</v>
+        <v>246.9471574737435</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34591,28 +34810,28 @@
         <v>0.0902</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1539746162101207</v>
+        <v>-0.1549597247652716</v>
       </c>
       <c r="J7" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K7" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06571674384896431</v>
+        <v>0.06739200258427447</v>
       </c>
       <c r="M7" t="n">
-        <v>3.412262534831134</v>
+        <v>3.395192700156169</v>
       </c>
       <c r="N7" t="n">
-        <v>18.99547832574781</v>
+        <v>18.87616770966712</v>
       </c>
       <c r="O7" t="n">
-        <v>4.358380241069819</v>
+        <v>4.344671185448575</v>
       </c>
       <c r="P7" t="n">
-        <v>249.0899134756284</v>
+        <v>249.1001974832302</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34663,28 +34882,28 @@
         <v>0.0733</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1906001000887868</v>
+        <v>-0.1907955004041217</v>
       </c>
       <c r="J8" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K8" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L8" t="n">
-        <v>0.121223077648993</v>
+        <v>0.1229850886483487</v>
       </c>
       <c r="M8" t="n">
-        <v>3.028697582623395</v>
+        <v>3.010549313259554</v>
       </c>
       <c r="N8" t="n">
-        <v>14.84188392781811</v>
+        <v>14.74606543717884</v>
       </c>
       <c r="O8" t="n">
-        <v>3.852516570738938</v>
+        <v>3.840060603321104</v>
       </c>
       <c r="P8" t="n">
-        <v>251.7812476729097</v>
+        <v>251.7832909202512</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34735,28 +34954,28 @@
         <v>0.0664</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2232332150080203</v>
+        <v>-0.2247664373884706</v>
       </c>
       <c r="J9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L9" t="n">
-        <v>0.123268478000008</v>
+        <v>0.1262637302212264</v>
       </c>
       <c r="M9" t="n">
-        <v>3.540342799998064</v>
+        <v>3.524258928504506</v>
       </c>
       <c r="N9" t="n">
-        <v>19.97476415803583</v>
+        <v>19.85866517687338</v>
       </c>
       <c r="O9" t="n">
-        <v>4.469313611510813</v>
+        <v>4.456306225661941</v>
       </c>
       <c r="P9" t="n">
-        <v>255.8293455357806</v>
+        <v>255.8453599634874</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34807,28 +35026,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1494958602200075</v>
+        <v>-0.1481939587669395</v>
       </c>
       <c r="J10" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K10" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05211193143658399</v>
+        <v>0.05194592597804359</v>
       </c>
       <c r="M10" t="n">
-        <v>3.693667349761224</v>
+        <v>3.675700976011631</v>
       </c>
       <c r="N10" t="n">
-        <v>22.91013585148195</v>
+        <v>22.76816326415058</v>
       </c>
       <c r="O10" t="n">
-        <v>4.78645336877755</v>
+        <v>4.771599654638954</v>
       </c>
       <c r="P10" t="n">
-        <v>256.9792236636596</v>
+        <v>256.965638882566</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34879,28 +35098,28 @@
         <v>0.0576</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1288946065475998</v>
+        <v>-0.129518105682904</v>
       </c>
       <c r="J11" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K11" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03936173546292943</v>
+        <v>0.04027716527754266</v>
       </c>
       <c r="M11" t="n">
-        <v>3.667960556485671</v>
+        <v>3.647994146504133</v>
       </c>
       <c r="N11" t="n">
-        <v>22.85096674437265</v>
+        <v>22.7056155302405</v>
       </c>
       <c r="O11" t="n">
-        <v>4.780268480365161</v>
+        <v>4.765040978862668</v>
       </c>
       <c r="P11" t="n">
-        <v>256.0614724012875</v>
+        <v>256.0679867254088</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34951,28 +35170,28 @@
         <v>0.0526</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1147760369404733</v>
+        <v>-0.1123584498200934</v>
       </c>
       <c r="J12" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K12" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02864202513143177</v>
+        <v>0.02784435730601409</v>
       </c>
       <c r="M12" t="n">
-        <v>4.016221193596678</v>
+        <v>4.001592413266441</v>
       </c>
       <c r="N12" t="n">
-        <v>25.17836258345065</v>
+        <v>25.03775939774956</v>
       </c>
       <c r="O12" t="n">
-        <v>5.017804558116094</v>
+        <v>5.003774515078548</v>
       </c>
       <c r="P12" t="n">
-        <v>255.7926076793984</v>
+        <v>255.7673776562415</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35023,28 +35242,28 @@
         <v>0.0537</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2916433576733292</v>
+        <v>-0.2939474841226843</v>
       </c>
       <c r="J13" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K13" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1709462687199077</v>
+        <v>0.1751329363616995</v>
       </c>
       <c r="M13" t="n">
-        <v>3.774007355533559</v>
+        <v>3.760533754657621</v>
       </c>
       <c r="N13" t="n">
-        <v>23.24752247392559</v>
+        <v>23.1175076240498</v>
       </c>
       <c r="O13" t="n">
-        <v>4.82156846616592</v>
+        <v>4.80806693215161</v>
       </c>
       <c r="P13" t="n">
-        <v>261.0244393923091</v>
+        <v>261.0484876939494</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35095,28 +35314,28 @@
         <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3625513888450382</v>
+        <v>-0.3691116115058712</v>
       </c>
       <c r="J14" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K14" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2389538095991685</v>
+        <v>0.2468835812023796</v>
       </c>
       <c r="M14" t="n">
-        <v>3.817693859193795</v>
+        <v>3.823520477331454</v>
       </c>
       <c r="N14" t="n">
-        <v>23.59313476405231</v>
+        <v>23.60862551197972</v>
       </c>
       <c r="O14" t="n">
-        <v>4.857276475974197</v>
+        <v>4.858870806265559</v>
       </c>
       <c r="P14" t="n">
-        <v>265.073683384487</v>
+        <v>265.1421451505522</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35167,28 +35386,28 @@
         <v>0.0466</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4363771052678012</v>
+        <v>-0.4463258995002429</v>
       </c>
       <c r="J15" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K15" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2171924430955486</v>
+        <v>0.2257157993822014</v>
       </c>
       <c r="M15" t="n">
-        <v>5.156130862895071</v>
+        <v>5.181139196245205</v>
       </c>
       <c r="N15" t="n">
-        <v>38.67974993168106</v>
+        <v>38.81753891460039</v>
       </c>
       <c r="O15" t="n">
-        <v>6.219304618016475</v>
+        <v>6.23037229341878</v>
       </c>
       <c r="P15" t="n">
-        <v>267.6832632773559</v>
+        <v>267.7870852216292</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35239,28 +35458,28 @@
         <v>0.0412</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5936098290390943</v>
+        <v>-0.6054748479493972</v>
       </c>
       <c r="J16" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K16" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3260948238240189</v>
+        <v>0.3350666367388438</v>
       </c>
       <c r="M16" t="n">
-        <v>5.26205490542104</v>
+        <v>5.295543724038175</v>
       </c>
       <c r="N16" t="n">
-        <v>41.03991932098051</v>
+        <v>41.32611050715054</v>
       </c>
       <c r="O16" t="n">
-        <v>6.406240654313613</v>
+        <v>6.428538753647716</v>
       </c>
       <c r="P16" t="n">
-        <v>274.2515006900201</v>
+        <v>274.3753210820894</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35311,28 +35530,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4976062134444443</v>
+        <v>-0.5082753477629842</v>
       </c>
       <c r="J17" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K17" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L17" t="n">
-        <v>0.22386576220417</v>
+        <v>0.2322466265603558</v>
       </c>
       <c r="M17" t="n">
-        <v>5.416658994499208</v>
+        <v>5.430138114466171</v>
       </c>
       <c r="N17" t="n">
-        <v>48.38048276704386</v>
+        <v>48.51273866630909</v>
       </c>
       <c r="O17" t="n">
-        <v>6.955608008437785</v>
+        <v>6.965108661486129</v>
       </c>
       <c r="P17" t="n">
-        <v>277.3399128581967</v>
+        <v>277.4512540926802</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35383,28 +35602,28 @@
         <v>0.0308</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3193286257563056</v>
+        <v>-0.3353508565317169</v>
       </c>
       <c r="J18" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K18" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06253273006758986</v>
+        <v>0.0687008491071891</v>
       </c>
       <c r="M18" t="n">
-        <v>7.323690858305167</v>
+        <v>7.361891892127189</v>
       </c>
       <c r="N18" t="n">
-        <v>86.15368796674451</v>
+        <v>86.59869015807796</v>
       </c>
       <c r="O18" t="n">
-        <v>9.281901096582775</v>
+        <v>9.305841722169895</v>
       </c>
       <c r="P18" t="n">
-        <v>279.7566581669277</v>
+        <v>279.9238775964371</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35442,7 +35661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S460"/>
+  <dimension ref="A1:S463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80065,6 +80284,297 @@
         </is>
       </c>
     </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>-40.72989249786032,172.69699808062353</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>-40.72934447263923,172.69638250210878</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>-40.72872740526416,172.69586799300703</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-40.72822356630312,172.69551594034013</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-40.72755337380319,172.69516784037685</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>-40.72690440282123,172.6948485168073</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>-40.72621170101068,172.69458542667505</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>-40.725518055696696,172.69432604807164</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>-40.72486346063908,172.69413720545006</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>-40.72416046793353,172.69392803921855</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>-40.7234512134605,172.69375756066003</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>-40.72274275374607,172.69350173172296</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>-40.72204710338563,172.69326437454734</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>-40.72134992074388,172.6930233826619</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>-40.72064284447285,172.6928132764906</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>-40.719927952189295,172.6926686666366</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>-40.719219118432676,172.692491877488</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>-40.72989081869766,172.69700055492834</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>-40.729343872942934,172.69638338578727</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>-40.728729566082045,172.69586481403655</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-40.728224170794704,172.6955139624653</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>-40.72755431360934,172.69516476344216</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>-40.72690440282123,172.6948485168073</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-40.726212504087904,172.69458215893312</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>-40.72552077009148,172.69431500570457</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>-40.7248636076068,172.6941362780613</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>-40.724161863878585,172.69391922904987</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>-40.723451489274964,172.6937558219113</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>-40.72274362786019,172.69349689311738</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>-40.72204651190545,172.69326771918318</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>-40.72134886120486,172.69302938019678</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>-40.72064106142155,172.6928229424148</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>-40.71992699698953,172.6926738447569</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>-40.71922104826973,172.69248140571906</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>-40.72989093863785,172.69700037819229</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>-40.72934585194068,172.6963804696481</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>-40.728733647626676,172.695858809314</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-40.72822568202353,172.69550901777814</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>-40.72755659599535,172.69515729088613</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>-40.72690556590904,172.69484378417084</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-40.7262134456266,172.6945783277873</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>-40.725523706068316,172.69430306191876</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>-40.724864140364716,172.69413291627697</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>-40.724162616953926,172.69391447619557</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>-40.72345156282549,172.693755358245</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>-40.72274333648885,172.69349850598593</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>-40.7220459000293,172.69327117915125</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>-40.72134731264726,172.69303814582435</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>-40.72063993640067,172.6928290411524</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>-40.71992570216279,172.69268086398642</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>-40.71922060292281,172.6924838222812</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0574/nzd0574.xlsx
+++ b/data/nzd0574/nzd0574.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S463"/>
+  <dimension ref="A1:S465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29629,6 +29629,132 @@
         <v>258.51</v>
       </c>
       <c r="S463" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="C464" t="n">
+        <v>234.42</v>
+      </c>
+      <c r="D464" t="n">
+        <v>246.99</v>
+      </c>
+      <c r="E464" t="n">
+        <v>242.6</v>
+      </c>
+      <c r="F464" t="n">
+        <v>242.61</v>
+      </c>
+      <c r="G464" t="n">
+        <v>244.46</v>
+      </c>
+      <c r="H464" t="n">
+        <v>246.59</v>
+      </c>
+      <c r="I464" t="n">
+        <v>248.13</v>
+      </c>
+      <c r="J464" t="n">
+        <v>254.2</v>
+      </c>
+      <c r="K464" t="n">
+        <v>252.19</v>
+      </c>
+      <c r="L464" t="n">
+        <v>254.55</v>
+      </c>
+      <c r="M464" t="n">
+        <v>251.39</v>
+      </c>
+      <c r="N464" t="n">
+        <v>250.55</v>
+      </c>
+      <c r="O464" t="n">
+        <v>248.92</v>
+      </c>
+      <c r="P464" t="n">
+        <v>249.74</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>256.25</v>
+      </c>
+      <c r="R464" t="n">
+        <v>258.51</v>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>233.91</v>
+      </c>
+      <c r="C465" t="n">
+        <v>234.99</v>
+      </c>
+      <c r="D465" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="E465" t="n">
+        <v>243.09</v>
+      </c>
+      <c r="F465" t="n">
+        <v>242.91</v>
+      </c>
+      <c r="G465" t="n">
+        <v>244.99</v>
+      </c>
+      <c r="H465" t="n">
+        <v>247.29</v>
+      </c>
+      <c r="I465" t="n">
+        <v>248.35</v>
+      </c>
+      <c r="J465" t="n">
+        <v>254.43</v>
+      </c>
+      <c r="K465" t="n">
+        <v>252.78</v>
+      </c>
+      <c r="L465" t="n">
+        <v>255.03</v>
+      </c>
+      <c r="M465" t="n">
+        <v>252.17</v>
+      </c>
+      <c r="N465" t="n">
+        <v>251.03</v>
+      </c>
+      <c r="O465" t="n">
+        <v>249.39</v>
+      </c>
+      <c r="P465" t="n">
+        <v>249.3</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>254.73</v>
+      </c>
+      <c r="R465" t="n">
+        <v>256.6</v>
+      </c>
+      <c r="S465" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29645,7 +29771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B464"/>
+  <dimension ref="A1:B466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34288,6 +34414,26 @@
       </c>
       <c r="B464" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>
@@ -34450,28 +34596,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1733167073608332</v>
+        <v>0.169918687341101</v>
       </c>
       <c r="J2" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K2" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09220662335965768</v>
+        <v>0.08938185073163651</v>
       </c>
       <c r="M2" t="n">
-        <v>3.314340069123434</v>
+        <v>3.315823725463068</v>
       </c>
       <c r="N2" t="n">
-        <v>16.79929792655795</v>
+        <v>16.79624415784964</v>
       </c>
       <c r="O2" t="n">
-        <v>4.098694661298637</v>
+        <v>4.09832211494529</v>
       </c>
       <c r="P2" t="n">
-        <v>232.9938985156181</v>
+        <v>233.0294675100462</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34522,28 +34668,28 @@
         <v>0.0863</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04523750060248707</v>
+        <v>0.04308265716563196</v>
       </c>
       <c r="J3" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K3" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007385192402737384</v>
+        <v>0.006754541006193104</v>
       </c>
       <c r="M3" t="n">
-        <v>3.299461648832975</v>
+        <v>3.294862701910983</v>
       </c>
       <c r="N3" t="n">
-        <v>15.62433421571639</v>
+        <v>15.58506575434328</v>
       </c>
       <c r="O3" t="n">
-        <v>3.95276285852268</v>
+        <v>3.947792516627905</v>
       </c>
       <c r="P3" t="n">
-        <v>236.0479847944795</v>
+        <v>236.070540379322</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34594,28 +34740,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007329706020677251</v>
+        <v>0.00519575773676226</v>
       </c>
       <c r="J4" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K4" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001848219566994436</v>
+        <v>9.361241594407765e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.385237514547858</v>
+        <v>3.381034497417253</v>
       </c>
       <c r="N4" t="n">
-        <v>16.50914779199273</v>
+        <v>16.46518468368587</v>
       </c>
       <c r="O4" t="n">
-        <v>4.063145061647778</v>
+        <v>4.057731470130308</v>
       </c>
       <c r="P4" t="n">
-        <v>249.2744036353057</v>
+        <v>249.2967418745359</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34666,28 +34812,28 @@
         <v>0.0901</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03104463807878012</v>
+        <v>-0.03391627777704354</v>
       </c>
       <c r="J5" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K5" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003333873261269882</v>
+        <v>0.004002368559094971</v>
       </c>
       <c r="M5" t="n">
-        <v>3.278209692349306</v>
+        <v>3.277874320079251</v>
       </c>
       <c r="N5" t="n">
-        <v>16.36662741525729</v>
+        <v>16.34558715984026</v>
       </c>
       <c r="O5" t="n">
-        <v>4.045568861761877</v>
+        <v>4.042967617955931</v>
       </c>
       <c r="P5" t="n">
-        <v>247.0798577141898</v>
+        <v>247.1099168419218</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34738,28 +34884,28 @@
         <v>0.0813</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08453919113624651</v>
+        <v>-0.08616626996281568</v>
       </c>
       <c r="J6" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K6" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0232156152014229</v>
+        <v>0.02429877126860847</v>
       </c>
       <c r="M6" t="n">
-        <v>3.343262560306308</v>
+        <v>3.336575848231561</v>
       </c>
       <c r="N6" t="n">
-        <v>17.08126651829651</v>
+        <v>17.02354710752489</v>
       </c>
       <c r="O6" t="n">
-        <v>4.132948888904449</v>
+        <v>4.125960143715023</v>
       </c>
       <c r="P6" t="n">
-        <v>246.9471574737435</v>
+        <v>246.9641890116567</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34810,28 +34956,28 @@
         <v>0.0902</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1549597247652716</v>
+        <v>-0.1551517397088321</v>
       </c>
       <c r="J7" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K7" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06739200258427447</v>
+        <v>0.06814801365598422</v>
       </c>
       <c r="M7" t="n">
-        <v>3.395192700156169</v>
+        <v>3.38171897488028</v>
       </c>
       <c r="N7" t="n">
-        <v>18.87616770966712</v>
+        <v>18.79533038756253</v>
       </c>
       <c r="O7" t="n">
-        <v>4.344671185448575</v>
+        <v>4.335358161393651</v>
       </c>
       <c r="P7" t="n">
-        <v>249.1001974832302</v>
+        <v>249.1022063621366</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34882,28 +35028,28 @@
         <v>0.0733</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1907955004041217</v>
+        <v>-0.1905750481665252</v>
       </c>
       <c r="J8" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K8" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1229850886483487</v>
+        <v>0.1237583268907279</v>
       </c>
       <c r="M8" t="n">
-        <v>3.010549313259554</v>
+        <v>2.999201794387237</v>
       </c>
       <c r="N8" t="n">
-        <v>14.74606543717884</v>
+        <v>14.68332738984641</v>
       </c>
       <c r="O8" t="n">
-        <v>3.840060603321104</v>
+        <v>3.831883008371525</v>
       </c>
       <c r="P8" t="n">
-        <v>251.7832909202512</v>
+        <v>251.7809817530683</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34954,28 +35100,28 @@
         <v>0.0664</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2247664373884706</v>
+        <v>-0.2261105429723704</v>
       </c>
       <c r="J9" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K9" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1262637302212264</v>
+        <v>0.1285868527018769</v>
       </c>
       <c r="M9" t="n">
-        <v>3.524258928504506</v>
+        <v>3.515071906462397</v>
       </c>
       <c r="N9" t="n">
-        <v>19.85866517687338</v>
+        <v>19.78390866943643</v>
       </c>
       <c r="O9" t="n">
-        <v>4.456306225661941</v>
+        <v>4.447910595935627</v>
       </c>
       <c r="P9" t="n">
-        <v>255.8453599634874</v>
+        <v>255.8594295203047</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35026,28 +35172,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1481939587669395</v>
+        <v>-0.1470872399139732</v>
       </c>
       <c r="J10" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K10" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05194592597804359</v>
+        <v>0.05166105924406261</v>
       </c>
       <c r="M10" t="n">
-        <v>3.675700976011631</v>
+        <v>3.664939526228571</v>
       </c>
       <c r="N10" t="n">
-        <v>22.76816326415058</v>
+        <v>22.67739714068605</v>
       </c>
       <c r="O10" t="n">
-        <v>4.771599654638954</v>
+        <v>4.762079077533893</v>
       </c>
       <c r="P10" t="n">
-        <v>256.965638882566</v>
+        <v>256.9540533096277</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35098,28 +35244,28 @@
         <v>0.0576</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.129518105682904</v>
+        <v>-0.1296140332458731</v>
       </c>
       <c r="J11" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K11" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04027716527754266</v>
+        <v>0.04070372256395127</v>
       </c>
       <c r="M11" t="n">
-        <v>3.647994146504133</v>
+        <v>3.63354964041108</v>
       </c>
       <c r="N11" t="n">
-        <v>22.7056155302405</v>
+        <v>22.60818044937586</v>
       </c>
       <c r="O11" t="n">
-        <v>4.765040978862668</v>
+        <v>4.754806036987824</v>
       </c>
       <c r="P11" t="n">
-        <v>256.0679867254088</v>
+        <v>256.0689896381185</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35170,28 +35316,28 @@
         <v>0.0526</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1123584498200934</v>
+        <v>-0.1106485723842812</v>
       </c>
       <c r="J12" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K12" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02784435730601409</v>
+        <v>0.02725863659055261</v>
       </c>
       <c r="M12" t="n">
-        <v>4.001592413266441</v>
+        <v>3.992416941488766</v>
       </c>
       <c r="N12" t="n">
-        <v>25.03775939774956</v>
+        <v>24.94754502124558</v>
       </c>
       <c r="O12" t="n">
-        <v>5.003774515078548</v>
+        <v>4.994751747709348</v>
       </c>
       <c r="P12" t="n">
-        <v>255.7673776562415</v>
+        <v>255.749477727171</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35242,28 +35388,28 @@
         <v>0.0537</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2939474841226843</v>
+        <v>-0.2951354668002223</v>
       </c>
       <c r="J13" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K13" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1751329363616995</v>
+        <v>0.1776300001565191</v>
       </c>
       <c r="M13" t="n">
-        <v>3.760533754657621</v>
+        <v>3.749997843177848</v>
       </c>
       <c r="N13" t="n">
-        <v>23.1175076240498</v>
+        <v>23.02696382444035</v>
       </c>
       <c r="O13" t="n">
-        <v>4.80806693215161</v>
+        <v>4.798641872909495</v>
       </c>
       <c r="P13" t="n">
-        <v>261.0484876939494</v>
+        <v>261.0609217674664</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35314,28 +35460,28 @@
         <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3691116115058712</v>
+        <v>-0.3728896113507624</v>
       </c>
       <c r="J14" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K14" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2468835812023796</v>
+        <v>0.2517975163134805</v>
       </c>
       <c r="M14" t="n">
-        <v>3.823520477331454</v>
+        <v>3.824519021879385</v>
       </c>
       <c r="N14" t="n">
-        <v>23.60862551197972</v>
+        <v>23.59235003739037</v>
       </c>
       <c r="O14" t="n">
-        <v>4.858870806265559</v>
+        <v>4.857195696838905</v>
       </c>
       <c r="P14" t="n">
-        <v>265.1421451505522</v>
+        <v>265.1816920224121</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35386,28 +35532,28 @@
         <v>0.0466</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4463258995002429</v>
+        <v>-0.4519706845057728</v>
       </c>
       <c r="J15" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K15" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2257157993822014</v>
+        <v>0.2309551453034645</v>
       </c>
       <c r="M15" t="n">
-        <v>5.181139196245205</v>
+        <v>5.191655871552782</v>
       </c>
       <c r="N15" t="n">
-        <v>38.81753891460039</v>
+        <v>38.84073982496088</v>
       </c>
       <c r="O15" t="n">
-        <v>6.23037229341878</v>
+        <v>6.232233935352626</v>
       </c>
       <c r="P15" t="n">
-        <v>267.7870852216292</v>
+        <v>267.8461735011088</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35458,28 +35604,28 @@
         <v>0.0412</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6054748479493972</v>
+        <v>-0.6127813927446197</v>
       </c>
       <c r="J16" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K16" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3350666367388438</v>
+        <v>0.340836161701732</v>
       </c>
       <c r="M16" t="n">
-        <v>5.295543724038175</v>
+        <v>5.314545391948149</v>
       </c>
       <c r="N16" t="n">
-        <v>41.32611050715054</v>
+        <v>41.46691993122136</v>
       </c>
       <c r="O16" t="n">
-        <v>6.428538753647716</v>
+        <v>6.43948134023396</v>
       </c>
       <c r="P16" t="n">
-        <v>274.3753210820894</v>
+        <v>274.4518064976157</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35530,28 +35676,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5082753477629842</v>
+        <v>-0.5153323315321584</v>
       </c>
       <c r="J17" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K17" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2322466265603558</v>
+        <v>0.2378034550278911</v>
       </c>
       <c r="M17" t="n">
-        <v>5.430138114466171</v>
+        <v>5.438903649208314</v>
       </c>
       <c r="N17" t="n">
-        <v>48.51273866630909</v>
+        <v>48.60338626036426</v>
       </c>
       <c r="O17" t="n">
-        <v>6.965108661486129</v>
+        <v>6.971612888016966</v>
       </c>
       <c r="P17" t="n">
-        <v>277.4512540926802</v>
+        <v>277.5251293981144</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35602,28 +35748,28 @@
         <v>0.0308</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3353508565317169</v>
+        <v>-0.3466583956513019</v>
       </c>
       <c r="J18" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K18" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0687008491071891</v>
+        <v>0.07311238638485018</v>
       </c>
       <c r="M18" t="n">
-        <v>7.361891892127189</v>
+        <v>7.390570982190946</v>
       </c>
       <c r="N18" t="n">
-        <v>86.59869015807796</v>
+        <v>86.99263702641449</v>
       </c>
       <c r="O18" t="n">
-        <v>9.305841722169895</v>
+        <v>9.326984347923743</v>
       </c>
       <c r="P18" t="n">
-        <v>279.9238775964371</v>
+        <v>280.0422483081351</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35661,7 +35807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S463"/>
+  <dimension ref="A1:S465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80575,6 +80721,200 @@
         </is>
       </c>
     </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>-40.729888299953586,172.69700426638533</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>-40.72934393291256,172.6963832974194</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>-40.728730646490945,172.69586322455123</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-40.72822420437756,172.69551385258336</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>-40.72755548836691,172.69516091727368</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>-40.72690409820296,172.6948497563073</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>-40.726212421010956,172.6945824969754</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>-40.72552234887163,172.6943085831029</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>-40.72486338715521,172.69413766914445</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>-40.72416155162777,172.69392119974552</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>-40.72345156282549,172.693755358245</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>-40.72274333648885,172.69349850598593</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>-40.7220459000293,172.69327117915125</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>-40.72134731264726,172.69303814582435</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>-40.72063993640067,172.6928290411524</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>-40.71992570216279,172.69268086398642</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>-40.71922060292281,172.6924838222812</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>-40.72988464177745,172.69700965683424</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>-40.729340514643575,172.69638833438668</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>-40.72873118669539,172.69586242980859</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-40.72822255881705,172.69551923679805</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-40.727554481431866,172.69516421398953</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>-40.726902630496554,172.69485572844343</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>-40.72621048254851,172.6945903846282</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>-40.72552173951792,172.69431106200182</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>-40.72486296462298,172.69414033538715</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>-40.72416046793353,172.69392803921855</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>-40.723450680219095,172.69376092224078</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>-40.722741713133736,172.69350749196752</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>-40.72204492102722,172.6932767151</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>-40.721346354986295,172.69304356667277</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>-40.72064087038029,172.69282397804952</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>-40.7199289286155,172.69266337344678</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>-40.71922465345728,172.69246184307224</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0574/nzd0574.xlsx
+++ b/data/nzd0574/nzd0574.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S465"/>
+  <dimension ref="A1:S468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29755,6 +29755,195 @@
         <v>256.6</v>
       </c>
       <c r="S465" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>234.85</v>
+      </c>
+      <c r="C466" t="n">
+        <v>234.94</v>
+      </c>
+      <c r="D466" t="n">
+        <v>247.09</v>
+      </c>
+      <c r="E466" t="n">
+        <v>243.98</v>
+      </c>
+      <c r="F466" t="n">
+        <v>243.34</v>
+      </c>
+      <c r="G466" t="n">
+        <v>245.55</v>
+      </c>
+      <c r="H466" t="n">
+        <v>247.6</v>
+      </c>
+      <c r="I466" t="n">
+        <v>248.88</v>
+      </c>
+      <c r="J466" t="n">
+        <v>254.24</v>
+      </c>
+      <c r="K466" t="n">
+        <v>253.08</v>
+      </c>
+      <c r="L466" t="n">
+        <v>254.69</v>
+      </c>
+      <c r="M466" t="n">
+        <v>253.34</v>
+      </c>
+      <c r="N466" t="n">
+        <v>252.51</v>
+      </c>
+      <c r="O466" t="n">
+        <v>252.22</v>
+      </c>
+      <c r="P466" t="n">
+        <v>252.89</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>258.23</v>
+      </c>
+      <c r="R466" t="n">
+        <v>259.95</v>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>235.22</v>
+      </c>
+      <c r="C467" t="n">
+        <v>235</v>
+      </c>
+      <c r="D467" t="n">
+        <v>246.82</v>
+      </c>
+      <c r="E467" t="n">
+        <v>244.26</v>
+      </c>
+      <c r="F467" t="n">
+        <v>243.56</v>
+      </c>
+      <c r="G467" t="n">
+        <v>246.07</v>
+      </c>
+      <c r="H467" t="n">
+        <v>247.63</v>
+      </c>
+      <c r="I467" t="n">
+        <v>249.12</v>
+      </c>
+      <c r="J467" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="K467" t="n">
+        <v>253.52</v>
+      </c>
+      <c r="L467" t="n">
+        <v>254.68</v>
+      </c>
+      <c r="M467" t="n">
+        <v>253.85</v>
+      </c>
+      <c r="N467" t="n">
+        <v>252.58</v>
+      </c>
+      <c r="O467" t="n">
+        <v>252.22</v>
+      </c>
+      <c r="P467" t="n">
+        <v>252.89</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>258.23</v>
+      </c>
+      <c r="R467" t="n">
+        <v>259.95</v>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>235.95</v>
+      </c>
+      <c r="C468" t="n">
+        <v>235.48</v>
+      </c>
+      <c r="D468" t="n">
+        <v>247.76</v>
+      </c>
+      <c r="E468" t="n">
+        <v>244.61</v>
+      </c>
+      <c r="F468" t="n">
+        <v>243.99</v>
+      </c>
+      <c r="G468" t="n">
+        <v>246.23</v>
+      </c>
+      <c r="H468" t="n">
+        <v>247.57</v>
+      </c>
+      <c r="I468" t="n">
+        <v>249.27</v>
+      </c>
+      <c r="J468" t="n">
+        <v>254.36</v>
+      </c>
+      <c r="K468" t="n">
+        <v>253.34</v>
+      </c>
+      <c r="L468" t="n">
+        <v>254.95</v>
+      </c>
+      <c r="M468" t="n">
+        <v>253.67</v>
+      </c>
+      <c r="N468" t="n">
+        <v>252.9</v>
+      </c>
+      <c r="O468" t="n">
+        <v>252.53</v>
+      </c>
+      <c r="P468" t="n">
+        <v>252.79</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>257.94</v>
+      </c>
+      <c r="R468" t="n">
+        <v>259.36</v>
+      </c>
+      <c r="S468" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29771,7 +29960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34434,6 +34623,36 @@
       </c>
       <c r="B466" t="n">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -34596,28 +34815,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.169918687341101</v>
+        <v>0.1670975256543808</v>
       </c>
       <c r="J2" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K2" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08938185073163651</v>
+        <v>0.0876684142575519</v>
       </c>
       <c r="M2" t="n">
-        <v>3.315823725463068</v>
+        <v>3.307392084005057</v>
       </c>
       <c r="N2" t="n">
-        <v>16.79624415784964</v>
+        <v>16.72162556801621</v>
       </c>
       <c r="O2" t="n">
-        <v>4.09832211494529</v>
+        <v>4.089208428047684</v>
       </c>
       <c r="P2" t="n">
-        <v>233.0294675100462</v>
+        <v>233.059137153872</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34668,28 +34887,28 @@
         <v>0.0863</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04308265716563196</v>
+        <v>0.04046844431098749</v>
       </c>
       <c r="J3" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K3" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006754541006193104</v>
+        <v>0.006038685017917933</v>
       </c>
       <c r="M3" t="n">
-        <v>3.294862701910983</v>
+        <v>3.28517319483859</v>
       </c>
       <c r="N3" t="n">
-        <v>15.58506575434328</v>
+        <v>15.51275811585361</v>
       </c>
       <c r="O3" t="n">
-        <v>3.947792516627905</v>
+        <v>3.938623886061427</v>
       </c>
       <c r="P3" t="n">
-        <v>236.070540379322</v>
+        <v>236.098036534058</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34740,28 +34959,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00519575773676226</v>
+        <v>0.002425053447002487</v>
       </c>
       <c r="J4" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K4" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L4" t="n">
-        <v>9.361241594407765e-05</v>
+        <v>2.06467314634029e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.381034497417253</v>
+        <v>3.372577981595226</v>
       </c>
       <c r="N4" t="n">
-        <v>16.46518468368587</v>
+        <v>16.39121889331318</v>
       </c>
       <c r="O4" t="n">
-        <v>4.057731470130308</v>
+        <v>4.048607031228541</v>
       </c>
       <c r="P4" t="n">
-        <v>249.2967418745359</v>
+        <v>249.3258839494603</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34812,28 +35031,28 @@
         <v>0.0901</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03391627777704354</v>
+        <v>-0.03631363304460879</v>
       </c>
       <c r="J5" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K5" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004002368559094971</v>
+        <v>0.004644266987105183</v>
       </c>
       <c r="M5" t="n">
-        <v>3.277874320079251</v>
+        <v>3.268245115933281</v>
       </c>
       <c r="N5" t="n">
-        <v>16.34558715984026</v>
+        <v>16.26407775976922</v>
       </c>
       <c r="O5" t="n">
-        <v>4.042967617955931</v>
+        <v>4.032874627330885</v>
       </c>
       <c r="P5" t="n">
-        <v>247.1099168419218</v>
+        <v>247.1351310876967</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34884,28 +35103,28 @@
         <v>0.0813</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08616626996281568</v>
+        <v>-0.08743921058018247</v>
       </c>
       <c r="J6" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K6" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02429877126860847</v>
+        <v>0.02534327868635489</v>
       </c>
       <c r="M6" t="n">
-        <v>3.336575848231561</v>
+        <v>3.321087533831431</v>
       </c>
       <c r="N6" t="n">
-        <v>17.02354710752489</v>
+        <v>16.92116403836365</v>
       </c>
       <c r="O6" t="n">
-        <v>4.125960143715023</v>
+        <v>4.113534251512153</v>
       </c>
       <c r="P6" t="n">
-        <v>246.9641890116567</v>
+        <v>246.977575320634</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34956,28 +35175,28 @@
         <v>0.0902</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1551517397088321</v>
+        <v>-0.1538775728620916</v>
       </c>
       <c r="J7" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K7" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06814801365598422</v>
+        <v>0.06798119415058956</v>
       </c>
       <c r="M7" t="n">
-        <v>3.38171897488028</v>
+        <v>3.366298672059354</v>
       </c>
       <c r="N7" t="n">
-        <v>18.79533038756253</v>
+        <v>18.68165889496883</v>
       </c>
       <c r="O7" t="n">
-        <v>4.335358161393651</v>
+        <v>4.322228463995029</v>
       </c>
       <c r="P7" t="n">
-        <v>249.1022063621366</v>
+        <v>249.0887986108299</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35028,28 +35247,28 @@
         <v>0.0733</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1905750481665252</v>
+        <v>-0.1893983981111089</v>
       </c>
       <c r="J8" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K8" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1237583268907279</v>
+        <v>0.1239182038788957</v>
       </c>
       <c r="M8" t="n">
-        <v>2.999201794387237</v>
+        <v>2.986444829699548</v>
       </c>
       <c r="N8" t="n">
-        <v>14.68332738984641</v>
+        <v>14.5945613404194</v>
       </c>
       <c r="O8" t="n">
-        <v>3.831883008371525</v>
+        <v>3.820282887486135</v>
       </c>
       <c r="P8" t="n">
-        <v>251.7809817530683</v>
+        <v>251.7686044574484</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35100,28 +35319,28 @@
         <v>0.0664</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2261105429723704</v>
+        <v>-0.2269820386020168</v>
       </c>
       <c r="J9" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K9" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1285868527018769</v>
+        <v>0.131046096813993</v>
       </c>
       <c r="M9" t="n">
-        <v>3.515071906462397</v>
+        <v>3.496372434132146</v>
       </c>
       <c r="N9" t="n">
-        <v>19.78390866943643</v>
+        <v>19.66004599383251</v>
       </c>
       <c r="O9" t="n">
-        <v>4.447910595935627</v>
+        <v>4.433965042017416</v>
       </c>
       <c r="P9" t="n">
-        <v>255.8594295203047</v>
+        <v>255.8685943089809</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35172,28 +35391,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1470872399139732</v>
+        <v>-0.1454791084578575</v>
       </c>
       <c r="J10" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K10" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05166105924406261</v>
+        <v>0.05126046798050032</v>
       </c>
       <c r="M10" t="n">
-        <v>3.664939526228571</v>
+        <v>3.648688797084351</v>
       </c>
       <c r="N10" t="n">
-        <v>22.67739714068605</v>
+        <v>22.54211125863934</v>
       </c>
       <c r="O10" t="n">
-        <v>4.762079077533893</v>
+        <v>4.747853331626762</v>
       </c>
       <c r="P10" t="n">
-        <v>256.9540533096277</v>
+        <v>256.9371363763867</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35244,28 +35463,28 @@
         <v>0.0576</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1296140332458731</v>
+        <v>-0.1286999560756832</v>
       </c>
       <c r="J11" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K11" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04070372256395127</v>
+        <v>0.04070091030442824</v>
       </c>
       <c r="M11" t="n">
-        <v>3.63354964041108</v>
+        <v>3.614779944531292</v>
       </c>
       <c r="N11" t="n">
-        <v>22.60818044937586</v>
+        <v>22.46650951028282</v>
       </c>
       <c r="O11" t="n">
-        <v>4.754806036987824</v>
+        <v>4.739884968043299</v>
       </c>
       <c r="P11" t="n">
-        <v>256.0689896381185</v>
+        <v>256.0593722095149</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35316,28 +35535,28 @@
         <v>0.0526</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1106485723842812</v>
+        <v>-0.1081509939518085</v>
       </c>
       <c r="J12" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K12" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02725863659055261</v>
+        <v>0.02641169815999356</v>
       </c>
       <c r="M12" t="n">
-        <v>3.992416941488766</v>
+        <v>3.978391039617724</v>
       </c>
       <c r="N12" t="n">
-        <v>24.94754502124558</v>
+        <v>24.8124099897751</v>
       </c>
       <c r="O12" t="n">
-        <v>4.994751747709348</v>
+        <v>4.981205676317241</v>
       </c>
       <c r="P12" t="n">
-        <v>255.749477727171</v>
+        <v>255.7232038641256</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35388,28 +35607,28 @@
         <v>0.0537</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2951354668002223</v>
+        <v>-0.2945203375535217</v>
       </c>
       <c r="J13" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K13" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1776300001565191</v>
+        <v>0.1790938049395427</v>
       </c>
       <c r="M13" t="n">
-        <v>3.749997843177848</v>
+        <v>3.729198155553606</v>
       </c>
       <c r="N13" t="n">
-        <v>23.02696382444035</v>
+        <v>22.88086536570784</v>
       </c>
       <c r="O13" t="n">
-        <v>4.798641872909495</v>
+        <v>4.783394753280126</v>
       </c>
       <c r="P13" t="n">
-        <v>261.0609217674664</v>
+        <v>261.0544484181558</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35460,28 +35679,28 @@
         <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3728896113507624</v>
+        <v>-0.3760168950703447</v>
       </c>
       <c r="J14" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K14" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2517975163134805</v>
+        <v>0.2573503775518979</v>
       </c>
       <c r="M14" t="n">
-        <v>3.824519021879385</v>
+        <v>3.814335354086343</v>
       </c>
       <c r="N14" t="n">
-        <v>23.59235003739037</v>
+        <v>23.4802528605717</v>
       </c>
       <c r="O14" t="n">
-        <v>4.857195696838905</v>
+        <v>4.845642667445847</v>
       </c>
       <c r="P14" t="n">
-        <v>265.1816920224121</v>
+        <v>265.2145859032944</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35532,28 +35751,28 @@
         <v>0.0466</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4519706845057728</v>
+        <v>-0.4561991419019474</v>
       </c>
       <c r="J15" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K15" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2309551453034645</v>
+        <v>0.2365077816233082</v>
       </c>
       <c r="M15" t="n">
-        <v>5.191655871552782</v>
+        <v>5.182661396237111</v>
       </c>
       <c r="N15" t="n">
-        <v>38.84073982496088</v>
+        <v>38.66312961121552</v>
       </c>
       <c r="O15" t="n">
-        <v>6.232233935352626</v>
+        <v>6.217968286443371</v>
       </c>
       <c r="P15" t="n">
-        <v>267.8461735011088</v>
+        <v>267.8906513554518</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35604,28 +35823,28 @@
         <v>0.0412</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6127813927446197</v>
+        <v>-0.6192084338141981</v>
       </c>
       <c r="J16" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K16" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L16" t="n">
-        <v>0.340836161701732</v>
+        <v>0.3478560979380966</v>
       </c>
       <c r="M16" t="n">
-        <v>5.314545391948149</v>
+        <v>5.316772642496663</v>
       </c>
       <c r="N16" t="n">
-        <v>41.46691993122136</v>
+        <v>41.36627734685783</v>
       </c>
       <c r="O16" t="n">
-        <v>6.43948134023396</v>
+        <v>6.431662098311588</v>
       </c>
       <c r="P16" t="n">
-        <v>274.4518064976157</v>
+        <v>274.5194137817132</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35676,28 +35895,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5153323315321584</v>
+        <v>-0.5222748229288303</v>
       </c>
       <c r="J17" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K17" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2378034550278911</v>
+        <v>0.2445759705933377</v>
       </c>
       <c r="M17" t="n">
-        <v>5.438903649208314</v>
+        <v>5.435862874207085</v>
       </c>
       <c r="N17" t="n">
-        <v>48.60338626036426</v>
+        <v>48.48463018099947</v>
       </c>
       <c r="O17" t="n">
-        <v>6.971612888016966</v>
+        <v>6.96309056245856</v>
       </c>
       <c r="P17" t="n">
-        <v>277.5251293981144</v>
+        <v>277.5981598513147</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35748,28 +35967,28 @@
         <v>0.0308</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3466583956513019</v>
+        <v>-0.3604038119020858</v>
       </c>
       <c r="J18" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K18" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L18" t="n">
-        <v>0.07311238638485018</v>
+        <v>0.0789601804596215</v>
       </c>
       <c r="M18" t="n">
-        <v>7.390570982190946</v>
+        <v>7.416464574894154</v>
       </c>
       <c r="N18" t="n">
-        <v>86.99263702641449</v>
+        <v>87.19225759809146</v>
       </c>
       <c r="O18" t="n">
-        <v>9.326984347923743</v>
+        <v>9.337679454665997</v>
       </c>
       <c r="P18" t="n">
-        <v>280.0422483081351</v>
+        <v>280.1868414156245</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35807,7 +36026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S465"/>
+  <dimension ref="A1:S468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80915,6 +81134,297 @@
         </is>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>-40.72987900458748,172.69701796342648</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>-40.72934081449174,172.69638789254748</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>-40.72873004626378,172.69586410759865</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-40.728219569941196,172.69552901628936</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-40.72755303815813,172.6951689392821</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>-40.726901079712114,172.69486203862476</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>-40.726209624086394,172.69459387773145</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>-40.725520271529255,172.6943170338945</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>-40.72486331367135,172.69413813283884</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>-40.724159916902394,172.6939315169166</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>-40.72345130539865,172.69375698107712</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>-40.72273927809977,172.69352097093912</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>-40.72204190243583,172.6932937842744</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>-40.72134058863939,172.69307620709728</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>-40.720633249949145,172.69286528836238</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>-40.71992149927963,172.69270364771313</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>-40.71921754911394,172.69250039299197</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>-40.7298767856934,172.6970212330422</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>-40.72934045467395,172.69638842275452</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>-40.7287316668771,172.69586172337063</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-40.728218629620535,172.69553209298306</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>-40.727552299738925,172.69517135687354</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>-40.72689963969766,172.6948678980786</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>-40.72620954100941,172.69459421577372</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>-40.72551960677956,172.6943197381477</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>-40.72486325855846,172.6941384806096</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>-40.72415910872322,172.6939366175403</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>-40.72345132378627,172.69375686516054</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>-40.72273821667421,172.69352684638798</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>-40.72204175966455,172.69329459160016</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>-40.72134058863939,172.69307620709728</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>-40.720633249949145,172.69286528836238</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>-40.71992149927963,172.69270364771313</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>-40.71921754911394,172.69250039299197</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>-40.729872407875064,172.697027683905</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>-40.72933757613147,172.69639266441075</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>-40.72872602474158,172.69587002401585</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-40.72821745421958,172.6955359388501</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-40.7275508564649,172.69517608216577</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>-40.72689919661622,172.69486970098743</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>-40.72620970716337,172.6945935396892</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>-40.72551919131097,172.69432142830595</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>-40.72486309321974,172.694139523922</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>-40.724159439342,172.69393453092152</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>-40.72345082732018,172.69375999490816</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>-40.72273859129503,172.6935247727002</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>-40.72204110699578,172.69329828223226</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>-40.72133995698954,172.6930797825498</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>-40.720633462217634,172.69286413765744</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>-40.71992211485371,172.69270031070283</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>-40.71921880032758,172.69249360360368</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
